--- a/Navdeep Singh.xlsx
+++ b/Navdeep Singh.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Project\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Asus\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{58EEC2E2-0763-4DA4-AB13-85789B9F75CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F8E19B8-EF7E-4F9B-8540-62991FFFA008}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="65">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -206,6 +206,30 @@
   </si>
   <si>
     <t>Doing more practicals today.</t>
+  </si>
+  <si>
+    <t>moslty induction</t>
+  </si>
+  <si>
+    <t>Satisfied</t>
+  </si>
+  <si>
+    <t>Mostly practicals</t>
+  </si>
+  <si>
+    <t>Weather help to handel the day</t>
+  </si>
+  <si>
+    <t>meet old friends</t>
+  </si>
+  <si>
+    <t>High</t>
+  </si>
+  <si>
+    <t>I went home at time</t>
+  </si>
+  <si>
+    <t>Excellent</t>
   </si>
 </sst>
 </file>
@@ -666,186 +690,186 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:A39"/>
-  <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="105" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="23.25" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:1" ht="22.8" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" s="4"/>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7" s="4"/>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A12" s="4"/>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A16" s="4"/>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" s="5" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A20" s="4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A22" s="4" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A23" s="4" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A24" s="4" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A25" s="4" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A26" s="4" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A27" s="4" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A28" s="4" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A29" s="4" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A30" s="4" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A31" s="4" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A32" s="4"/>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A33" s="5" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A34" s="4" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A35" s="4" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A36" s="4"/>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A37" s="5"/>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A38" s="4"/>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A39" s="4"/>
     </row>
   </sheetData>
@@ -857,7 +881,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:N401"/>
-  <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="6" width="11" customWidth="1"/>
@@ -870,7 +894,7 @@
     <col min="14" max="14" width="28" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="19" t="s">
         <v>29</v>
       </c>
@@ -888,7 +912,7 @@
       <c r="M1" s="19"/>
       <c r="N1" s="19"/>
     </row>
-    <row r="2" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
         <v>30</v>
       </c>
@@ -905,7 +929,7 @@
       </c>
       <c r="G2" s="20"/>
     </row>
-    <row r="3" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
         <v>32</v>
       </c>
@@ -922,7 +946,7 @@
       </c>
       <c r="G3" s="20"/>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="18" t="s">
         <v>34</v>
       </c>
@@ -940,7 +964,7 @@
       <c r="M4" s="18"/>
       <c r="N4" s="18"/>
     </row>
-    <row r="5" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
         <v>35</v>
       </c>
@@ -984,7 +1008,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="6" spans="1:14" ht="28.5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6" s="8">
         <v>46245</v>
       </c>
@@ -1004,7 +1028,7 @@
         <v>250</v>
       </c>
       <c r="G6" s="9">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H6" s="9">
         <v>300</v>
@@ -1030,117 +1054,237 @@
         <v>56</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A7" s="13"/>
-      <c r="B7" s="14"/>
-      <c r="C7" s="14"/>
-      <c r="D7" s="14"/>
-      <c r="E7" s="14"/>
-      <c r="F7" s="14"/>
-      <c r="G7" s="14"/>
-      <c r="H7" s="14"/>
-      <c r="I7" s="15" t="str">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A7" s="13">
+        <v>46246</v>
+      </c>
+      <c r="B7" s="14">
+        <v>360</v>
+      </c>
+      <c r="C7" s="14">
+        <v>20</v>
+      </c>
+      <c r="D7" s="14">
+        <v>50</v>
+      </c>
+      <c r="E7" s="14">
+        <v>50</v>
+      </c>
+      <c r="F7" s="14">
+        <v>200</v>
+      </c>
+      <c r="G7" s="14">
+        <v>4</v>
+      </c>
+      <c r="H7" s="14">
+        <v>240</v>
+      </c>
+      <c r="I7" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J7" s="15" t="str">
+        <v>920</v>
+      </c>
+      <c r="J7" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K7" s="16"/>
-      <c r="L7" s="16"/>
-      <c r="M7" s="16"/>
-      <c r="N7" s="17"/>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A8" s="13"/>
-      <c r="B8" s="14"/>
-      <c r="C8" s="14"/>
-      <c r="D8" s="14"/>
-      <c r="E8" s="14"/>
-      <c r="F8" s="14"/>
-      <c r="G8" s="14"/>
-      <c r="H8" s="14"/>
-      <c r="I8" s="15" t="str">
+        <v>520</v>
+      </c>
+      <c r="K7" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="L7" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="M7" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="N7" s="17" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A8" s="13">
+        <v>46247</v>
+      </c>
+      <c r="B8" s="14">
+        <v>380</v>
+      </c>
+      <c r="C8" s="14">
+        <v>15</v>
+      </c>
+      <c r="D8" s="14">
+        <v>70</v>
+      </c>
+      <c r="E8" s="14">
+        <v>50</v>
+      </c>
+      <c r="F8" s="14">
+        <v>300</v>
+      </c>
+      <c r="G8" s="14">
+        <v>6</v>
+      </c>
+      <c r="H8" s="14">
+        <v>300</v>
+      </c>
+      <c r="I8" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J8" s="15" t="str">
+        <v>1115</v>
+      </c>
+      <c r="J8" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K8" s="16"/>
-      <c r="L8" s="16"/>
-      <c r="M8" s="16"/>
-      <c r="N8" s="17"/>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A9" s="13"/>
-      <c r="B9" s="14"/>
-      <c r="C9" s="14"/>
-      <c r="D9" s="14"/>
-      <c r="E9" s="14"/>
-      <c r="F9" s="14"/>
-      <c r="G9" s="14"/>
-      <c r="H9" s="14"/>
-      <c r="I9" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J9" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K9" s="16"/>
-      <c r="L9" s="16"/>
-      <c r="M9" s="16"/>
-      <c r="N9" s="17"/>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A10" s="13"/>
-      <c r="B10" s="14"/>
-      <c r="C10" s="14"/>
-      <c r="D10" s="14"/>
-      <c r="E10" s="14"/>
-      <c r="F10" s="14"/>
-      <c r="G10" s="14"/>
-      <c r="H10" s="14"/>
-      <c r="I10" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J10" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K10" s="16"/>
-      <c r="L10" s="16"/>
-      <c r="M10" s="16"/>
-      <c r="N10" s="17"/>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A11" s="13"/>
-      <c r="B11" s="14"/>
-      <c r="C11" s="14"/>
-      <c r="D11" s="14"/>
-      <c r="E11" s="14"/>
-      <c r="F11" s="14"/>
-      <c r="G11" s="14"/>
-      <c r="H11" s="14"/>
-      <c r="I11" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J11" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K11" s="16"/>
-      <c r="L11" s="16"/>
-      <c r="M11" s="16"/>
-      <c r="N11" s="17"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+        <v>325</v>
+      </c>
+      <c r="K8" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L8" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M8" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="N8" s="17" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A9" s="13">
+        <v>46248</v>
+      </c>
+      <c r="B9" s="14">
+        <v>360</v>
+      </c>
+      <c r="C9" s="14">
+        <v>30</v>
+      </c>
+      <c r="D9" s="14">
+        <v>80</v>
+      </c>
+      <c r="E9" s="14">
+        <v>0</v>
+      </c>
+      <c r="F9" s="14">
+        <v>200</v>
+      </c>
+      <c r="G9" s="14">
+        <v>4</v>
+      </c>
+      <c r="H9" s="14">
+        <v>300</v>
+      </c>
+      <c r="I9" s="15">
+        <f t="shared" ref="I9:I11" si="2">IF(SUM(B9:F9,H9)=0,"",SUM(B9:F9,H9))</f>
+        <v>970</v>
+      </c>
+      <c r="J9" s="15">
+        <f t="shared" ref="J9:J11" si="3">IF(I9="","",1440-I9)</f>
+        <v>470</v>
+      </c>
+      <c r="K9" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L9" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M9" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="N9" s="17" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A10" s="13">
+        <v>46251</v>
+      </c>
+      <c r="B10" s="14">
+        <v>400</v>
+      </c>
+      <c r="C10" s="14">
+        <v>30</v>
+      </c>
+      <c r="D10" s="14">
+        <v>50</v>
+      </c>
+      <c r="E10" s="14">
+        <v>50</v>
+      </c>
+      <c r="F10" s="14">
+        <v>250</v>
+      </c>
+      <c r="G10" s="14">
+        <v>4</v>
+      </c>
+      <c r="H10" s="14">
+        <v>300</v>
+      </c>
+      <c r="I10" s="15">
+        <f t="shared" si="2"/>
+        <v>1080</v>
+      </c>
+      <c r="J10" s="15">
+        <f t="shared" si="3"/>
+        <v>360</v>
+      </c>
+      <c r="K10" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="L10" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="M10" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="N10" s="17" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A11" s="13">
+        <v>46252</v>
+      </c>
+      <c r="B11" s="14">
+        <v>480</v>
+      </c>
+      <c r="C11" s="14">
+        <v>40</v>
+      </c>
+      <c r="D11" s="14">
+        <v>90</v>
+      </c>
+      <c r="E11" s="14">
+        <v>90</v>
+      </c>
+      <c r="F11" s="14">
+        <v>200</v>
+      </c>
+      <c r="G11" s="14">
+        <v>4</v>
+      </c>
+      <c r="H11" s="14">
+        <v>300</v>
+      </c>
+      <c r="I11" s="15">
+        <f t="shared" si="2"/>
+        <v>1200</v>
+      </c>
+      <c r="J11" s="15">
+        <f t="shared" si="3"/>
+        <v>240</v>
+      </c>
+      <c r="K11" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="L11" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M11" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="N11" s="17" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12" s="13"/>
       <c r="B12" s="14"/>
       <c r="C12" s="14"/>
@@ -1162,7 +1306,7 @@
       <c r="M12" s="16"/>
       <c r="N12" s="17"/>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13" s="13"/>
       <c r="B13" s="14"/>
       <c r="C13" s="14"/>
@@ -1184,7 +1328,7 @@
       <c r="M13" s="16"/>
       <c r="N13" s="17"/>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" s="13"/>
       <c r="B14" s="14"/>
       <c r="C14" s="14"/>
@@ -1206,7 +1350,7 @@
       <c r="M14" s="16"/>
       <c r="N14" s="17"/>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15" s="13"/>
       <c r="B15" s="14"/>
       <c r="C15" s="14"/>
@@ -1228,7 +1372,7 @@
       <c r="M15" s="16"/>
       <c r="N15" s="17"/>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A16" s="13"/>
       <c r="B16" s="14"/>
       <c r="C16" s="14"/>
@@ -1250,7 +1394,7 @@
       <c r="M16" s="16"/>
       <c r="N16" s="17"/>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A17" s="13"/>
       <c r="B17" s="14"/>
       <c r="C17" s="14"/>
@@ -1272,7 +1416,7 @@
       <c r="M17" s="16"/>
       <c r="N17" s="17"/>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A18" s="13"/>
       <c r="B18" s="14"/>
       <c r="C18" s="14"/>
@@ -1294,7 +1438,7 @@
       <c r="M18" s="16"/>
       <c r="N18" s="17"/>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A19" s="13"/>
       <c r="B19" s="14"/>
       <c r="C19" s="14"/>
@@ -1316,7 +1460,7 @@
       <c r="M19" s="16"/>
       <c r="N19" s="17"/>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A20" s="13"/>
       <c r="B20" s="14"/>
       <c r="C20" s="14"/>
@@ -1338,7 +1482,7 @@
       <c r="M20" s="16"/>
       <c r="N20" s="17"/>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A21" s="13"/>
       <c r="B21" s="14"/>
       <c r="C21" s="14"/>
@@ -1360,7 +1504,7 @@
       <c r="M21" s="16"/>
       <c r="N21" s="17"/>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A22" s="13"/>
       <c r="B22" s="14"/>
       <c r="C22" s="14"/>
@@ -1382,7 +1526,7 @@
       <c r="M22" s="16"/>
       <c r="N22" s="17"/>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A23" s="13"/>
       <c r="B23" s="14"/>
       <c r="C23" s="14"/>
@@ -1404,7 +1548,7 @@
       <c r="M23" s="16"/>
       <c r="N23" s="17"/>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A24" s="13"/>
       <c r="B24" s="14"/>
       <c r="C24" s="14"/>
@@ -1426,7 +1570,7 @@
       <c r="M24" s="16"/>
       <c r="N24" s="17"/>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A25" s="13"/>
       <c r="B25" s="14"/>
       <c r="C25" s="14"/>
@@ -1448,7 +1592,7 @@
       <c r="M25" s="16"/>
       <c r="N25" s="17"/>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A26" s="13"/>
       <c r="B26" s="14"/>
       <c r="C26" s="14"/>
@@ -1470,7 +1614,7 @@
       <c r="M26" s="16"/>
       <c r="N26" s="17"/>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A27" s="13"/>
       <c r="B27" s="14"/>
       <c r="C27" s="14"/>
@@ -1492,7 +1636,7 @@
       <c r="M27" s="16"/>
       <c r="N27" s="17"/>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A28" s="13"/>
       <c r="B28" s="14"/>
       <c r="C28" s="14"/>
@@ -1514,7 +1658,7 @@
       <c r="M28" s="16"/>
       <c r="N28" s="17"/>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A29" s="13"/>
       <c r="B29" s="14"/>
       <c r="C29" s="14"/>
@@ -1536,7 +1680,7 @@
       <c r="M29" s="16"/>
       <c r="N29" s="17"/>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A30" s="13"/>
       <c r="B30" s="14"/>
       <c r="C30" s="14"/>
@@ -1558,7 +1702,7 @@
       <c r="M30" s="16"/>
       <c r="N30" s="17"/>
     </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A31" s="13"/>
       <c r="B31" s="14"/>
       <c r="C31" s="14"/>
@@ -1580,7 +1724,7 @@
       <c r="M31" s="16"/>
       <c r="N31" s="17"/>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A32" s="13"/>
       <c r="B32" s="14"/>
       <c r="C32" s="14"/>
@@ -1602,7 +1746,7 @@
       <c r="M32" s="16"/>
       <c r="N32" s="17"/>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A33" s="13"/>
       <c r="B33" s="14"/>
       <c r="C33" s="14"/>
@@ -1624,7 +1768,7 @@
       <c r="M33" s="16"/>
       <c r="N33" s="17"/>
     </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A34" s="13"/>
       <c r="B34" s="14"/>
       <c r="C34" s="14"/>
@@ -1646,7 +1790,7 @@
       <c r="M34" s="16"/>
       <c r="N34" s="17"/>
     </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A35" s="13"/>
       <c r="B35" s="14"/>
       <c r="C35" s="14"/>
@@ -1668,7 +1812,7 @@
       <c r="M35" s="16"/>
       <c r="N35" s="17"/>
     </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A36" s="13"/>
       <c r="B36" s="14"/>
       <c r="C36" s="14"/>
@@ -1690,7 +1834,7 @@
       <c r="M36" s="16"/>
       <c r="N36" s="17"/>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A37" s="13"/>
       <c r="B37" s="14"/>
       <c r="C37" s="14"/>
@@ -1712,7 +1856,7 @@
       <c r="M37" s="16"/>
       <c r="N37" s="17"/>
     </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A38" s="13"/>
       <c r="B38" s="14"/>
       <c r="C38" s="14"/>
@@ -1734,7 +1878,7 @@
       <c r="M38" s="16"/>
       <c r="N38" s="17"/>
     </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A39" s="13"/>
       <c r="B39" s="14"/>
       <c r="C39" s="14"/>
@@ -1756,7 +1900,7 @@
       <c r="M39" s="16"/>
       <c r="N39" s="17"/>
     </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A40" s="13"/>
       <c r="B40" s="14"/>
       <c r="C40" s="14"/>
@@ -1778,7 +1922,7 @@
       <c r="M40" s="16"/>
       <c r="N40" s="17"/>
     </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A41" s="13"/>
       <c r="B41" s="14"/>
       <c r="C41" s="14"/>
@@ -1800,7 +1944,7 @@
       <c r="M41" s="16"/>
       <c r="N41" s="17"/>
     </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A42" s="13"/>
       <c r="B42" s="14"/>
       <c r="C42" s="14"/>
@@ -1822,7 +1966,7 @@
       <c r="M42" s="16"/>
       <c r="N42" s="17"/>
     </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A43" s="13"/>
       <c r="B43" s="14"/>
       <c r="C43" s="14"/>
@@ -1844,7 +1988,7 @@
       <c r="M43" s="16"/>
       <c r="N43" s="17"/>
     </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A44" s="13"/>
       <c r="B44" s="14"/>
       <c r="C44" s="14"/>
@@ -1866,7 +2010,7 @@
       <c r="M44" s="16"/>
       <c r="N44" s="17"/>
     </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A45" s="13"/>
       <c r="B45" s="14"/>
       <c r="C45" s="14"/>
@@ -1888,7 +2032,7 @@
       <c r="M45" s="16"/>
       <c r="N45" s="17"/>
     </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A46" s="13"/>
       <c r="B46" s="14"/>
       <c r="C46" s="14"/>
@@ -1910,7 +2054,7 @@
       <c r="M46" s="16"/>
       <c r="N46" s="17"/>
     </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A47" s="13"/>
       <c r="B47" s="14"/>
       <c r="C47" s="14"/>
@@ -1932,7 +2076,7 @@
       <c r="M47" s="16"/>
       <c r="N47" s="17"/>
     </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A48" s="13"/>
       <c r="B48" s="14"/>
       <c r="C48" s="14"/>
@@ -1954,7 +2098,7 @@
       <c r="M48" s="16"/>
       <c r="N48" s="17"/>
     </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A49" s="13"/>
       <c r="B49" s="14"/>
       <c r="C49" s="14"/>
@@ -1976,7 +2120,7 @@
       <c r="M49" s="16"/>
       <c r="N49" s="17"/>
     </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A50" s="13"/>
       <c r="B50" s="14"/>
       <c r="C50" s="14"/>
@@ -1998,7 +2142,7 @@
       <c r="M50" s="16"/>
       <c r="N50" s="17"/>
     </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A51" s="13"/>
       <c r="B51" s="14"/>
       <c r="C51" s="14"/>
@@ -2020,7 +2164,7 @@
       <c r="M51" s="16"/>
       <c r="N51" s="17"/>
     </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A52" s="13"/>
       <c r="B52" s="14"/>
       <c r="C52" s="14"/>
@@ -2042,7 +2186,7 @@
       <c r="M52" s="16"/>
       <c r="N52" s="17"/>
     </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A53" s="13"/>
       <c r="B53" s="14"/>
       <c r="C53" s="14"/>
@@ -2064,7 +2208,7 @@
       <c r="M53" s="16"/>
       <c r="N53" s="17"/>
     </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A54" s="13"/>
       <c r="B54" s="14"/>
       <c r="C54" s="14"/>
@@ -2086,7 +2230,7 @@
       <c r="M54" s="16"/>
       <c r="N54" s="17"/>
     </row>
-    <row r="55" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A55" s="13"/>
       <c r="B55" s="14"/>
       <c r="C55" s="14"/>
@@ -2108,7 +2252,7 @@
       <c r="M55" s="16"/>
       <c r="N55" s="17"/>
     </row>
-    <row r="56" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A56" s="13"/>
       <c r="B56" s="14"/>
       <c r="C56" s="14"/>
@@ -2130,7 +2274,7 @@
       <c r="M56" s="16"/>
       <c r="N56" s="17"/>
     </row>
-    <row r="57" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A57" s="13"/>
       <c r="B57" s="14"/>
       <c r="C57" s="14"/>
@@ -2152,7 +2296,7 @@
       <c r="M57" s="16"/>
       <c r="N57" s="17"/>
     </row>
-    <row r="58" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A58" s="13"/>
       <c r="B58" s="14"/>
       <c r="C58" s="14"/>
@@ -2174,7 +2318,7 @@
       <c r="M58" s="16"/>
       <c r="N58" s="17"/>
     </row>
-    <row r="59" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A59" s="13"/>
       <c r="B59" s="14"/>
       <c r="C59" s="14"/>
@@ -2196,7 +2340,7 @@
       <c r="M59" s="16"/>
       <c r="N59" s="17"/>
     </row>
-    <row r="60" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A60" s="13"/>
       <c r="B60" s="14"/>
       <c r="C60" s="14"/>
@@ -2218,7 +2362,7 @@
       <c r="M60" s="16"/>
       <c r="N60" s="17"/>
     </row>
-    <row r="61" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A61" s="13"/>
       <c r="B61" s="14"/>
       <c r="C61" s="14"/>
@@ -2240,7 +2384,7 @@
       <c r="M61" s="16"/>
       <c r="N61" s="17"/>
     </row>
-    <row r="62" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A62" s="13"/>
       <c r="B62" s="14"/>
       <c r="C62" s="14"/>
@@ -2262,7 +2406,7 @@
       <c r="M62" s="16"/>
       <c r="N62" s="17"/>
     </row>
-    <row r="63" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A63" s="13"/>
       <c r="B63" s="14"/>
       <c r="C63" s="14"/>
@@ -2284,7 +2428,7 @@
       <c r="M63" s="16"/>
       <c r="N63" s="17"/>
     </row>
-    <row r="64" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A64" s="13"/>
       <c r="B64" s="14"/>
       <c r="C64" s="14"/>
@@ -2306,7 +2450,7 @@
       <c r="M64" s="16"/>
       <c r="N64" s="17"/>
     </row>
-    <row r="65" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A65" s="13"/>
       <c r="B65" s="14"/>
       <c r="C65" s="14"/>
@@ -2328,7 +2472,7 @@
       <c r="M65" s="16"/>
       <c r="N65" s="17"/>
     </row>
-    <row r="66" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A66" s="13"/>
       <c r="B66" s="14"/>
       <c r="C66" s="14"/>
@@ -2350,7 +2494,7 @@
       <c r="M66" s="16"/>
       <c r="N66" s="17"/>
     </row>
-    <row r="67" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A67" s="13"/>
       <c r="B67" s="14"/>
       <c r="C67" s="14"/>
@@ -2372,7 +2516,7 @@
       <c r="M67" s="16"/>
       <c r="N67" s="17"/>
     </row>
-    <row r="68" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A68" s="13"/>
       <c r="B68" s="14"/>
       <c r="C68" s="14"/>
@@ -2394,7 +2538,7 @@
       <c r="M68" s="16"/>
       <c r="N68" s="17"/>
     </row>
-    <row r="69" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A69" s="13"/>
       <c r="B69" s="14"/>
       <c r="C69" s="14"/>
@@ -2416,7 +2560,7 @@
       <c r="M69" s="16"/>
       <c r="N69" s="17"/>
     </row>
-    <row r="70" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A70" s="13"/>
       <c r="B70" s="14"/>
       <c r="C70" s="14"/>
@@ -2426,11 +2570,11 @@
       <c r="G70" s="14"/>
       <c r="H70" s="14"/>
       <c r="I70" s="15" t="str">
-        <f t="shared" ref="I70:I133" si="2">IF(SUM(B70:F70,H70)=0,"",SUM(B70:F70,H70))</f>
+        <f t="shared" ref="I70:I133" si="4">IF(SUM(B70:F70,H70)=0,"",SUM(B70:F70,H70))</f>
         <v/>
       </c>
       <c r="J70" s="15" t="str">
-        <f t="shared" ref="J70:J133" si="3">IF(I70="","",1440-I70)</f>
+        <f t="shared" ref="J70:J133" si="5">IF(I70="","",1440-I70)</f>
         <v/>
       </c>
       <c r="K70" s="16"/>
@@ -2438,7 +2582,7 @@
       <c r="M70" s="16"/>
       <c r="N70" s="17"/>
     </row>
-    <row r="71" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A71" s="13"/>
       <c r="B71" s="14"/>
       <c r="C71" s="14"/>
@@ -2448,11 +2592,11 @@
       <c r="G71" s="14"/>
       <c r="H71" s="14"/>
       <c r="I71" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J71" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K71" s="16"/>
@@ -2460,7 +2604,7 @@
       <c r="M71" s="16"/>
       <c r="N71" s="17"/>
     </row>
-    <row r="72" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A72" s="13"/>
       <c r="B72" s="14"/>
       <c r="C72" s="14"/>
@@ -2470,11 +2614,11 @@
       <c r="G72" s="14"/>
       <c r="H72" s="14"/>
       <c r="I72" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J72" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K72" s="16"/>
@@ -2482,7 +2626,7 @@
       <c r="M72" s="16"/>
       <c r="N72" s="17"/>
     </row>
-    <row r="73" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A73" s="13"/>
       <c r="B73" s="14"/>
       <c r="C73" s="14"/>
@@ -2492,11 +2636,11 @@
       <c r="G73" s="14"/>
       <c r="H73" s="14"/>
       <c r="I73" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J73" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K73" s="16"/>
@@ -2504,7 +2648,7 @@
       <c r="M73" s="16"/>
       <c r="N73" s="17"/>
     </row>
-    <row r="74" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A74" s="13"/>
       <c r="B74" s="14"/>
       <c r="C74" s="14"/>
@@ -2514,11 +2658,11 @@
       <c r="G74" s="14"/>
       <c r="H74" s="14"/>
       <c r="I74" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J74" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K74" s="16"/>
@@ -2526,7 +2670,7 @@
       <c r="M74" s="16"/>
       <c r="N74" s="17"/>
     </row>
-    <row r="75" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A75" s="13"/>
       <c r="B75" s="14"/>
       <c r="C75" s="14"/>
@@ -2536,11 +2680,11 @@
       <c r="G75" s="14"/>
       <c r="H75" s="14"/>
       <c r="I75" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J75" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K75" s="16"/>
@@ -2548,7 +2692,7 @@
       <c r="M75" s="16"/>
       <c r="N75" s="17"/>
     </row>
-    <row r="76" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A76" s="13"/>
       <c r="B76" s="14"/>
       <c r="C76" s="14"/>
@@ -2558,11 +2702,11 @@
       <c r="G76" s="14"/>
       <c r="H76" s="14"/>
       <c r="I76" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J76" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K76" s="16"/>
@@ -2570,7 +2714,7 @@
       <c r="M76" s="16"/>
       <c r="N76" s="17"/>
     </row>
-    <row r="77" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A77" s="13"/>
       <c r="B77" s="14"/>
       <c r="C77" s="14"/>
@@ -2580,11 +2724,11 @@
       <c r="G77" s="14"/>
       <c r="H77" s="14"/>
       <c r="I77" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J77" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K77" s="16"/>
@@ -2592,7 +2736,7 @@
       <c r="M77" s="16"/>
       <c r="N77" s="17"/>
     </row>
-    <row r="78" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A78" s="13"/>
       <c r="B78" s="14"/>
       <c r="C78" s="14"/>
@@ -2602,11 +2746,11 @@
       <c r="G78" s="14"/>
       <c r="H78" s="14"/>
       <c r="I78" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J78" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K78" s="16"/>
@@ -2614,7 +2758,7 @@
       <c r="M78" s="16"/>
       <c r="N78" s="17"/>
     </row>
-    <row r="79" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A79" s="13"/>
       <c r="B79" s="14"/>
       <c r="C79" s="14"/>
@@ -2624,11 +2768,11 @@
       <c r="G79" s="14"/>
       <c r="H79" s="14"/>
       <c r="I79" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J79" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K79" s="16"/>
@@ -2636,7 +2780,7 @@
       <c r="M79" s="16"/>
       <c r="N79" s="17"/>
     </row>
-    <row r="80" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A80" s="13"/>
       <c r="B80" s="14"/>
       <c r="C80" s="14"/>
@@ -2646,11 +2790,11 @@
       <c r="G80" s="14"/>
       <c r="H80" s="14"/>
       <c r="I80" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J80" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K80" s="16"/>
@@ -2658,7 +2802,7 @@
       <c r="M80" s="16"/>
       <c r="N80" s="17"/>
     </row>
-    <row r="81" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A81" s="13"/>
       <c r="B81" s="14"/>
       <c r="C81" s="14"/>
@@ -2668,11 +2812,11 @@
       <c r="G81" s="14"/>
       <c r="H81" s="14"/>
       <c r="I81" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J81" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K81" s="16"/>
@@ -2680,7 +2824,7 @@
       <c r="M81" s="16"/>
       <c r="N81" s="17"/>
     </row>
-    <row r="82" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A82" s="13"/>
       <c r="B82" s="14"/>
       <c r="C82" s="14"/>
@@ -2690,11 +2834,11 @@
       <c r="G82" s="14"/>
       <c r="H82" s="14"/>
       <c r="I82" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J82" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K82" s="16"/>
@@ -2702,7 +2846,7 @@
       <c r="M82" s="16"/>
       <c r="N82" s="17"/>
     </row>
-    <row r="83" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A83" s="13"/>
       <c r="B83" s="14"/>
       <c r="C83" s="14"/>
@@ -2712,11 +2856,11 @@
       <c r="G83" s="14"/>
       <c r="H83" s="14"/>
       <c r="I83" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J83" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K83" s="16"/>
@@ -2724,7 +2868,7 @@
       <c r="M83" s="16"/>
       <c r="N83" s="17"/>
     </row>
-    <row r="84" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A84" s="13"/>
       <c r="B84" s="14"/>
       <c r="C84" s="14"/>
@@ -2734,11 +2878,11 @@
       <c r="G84" s="14"/>
       <c r="H84" s="14"/>
       <c r="I84" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J84" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K84" s="16"/>
@@ -2746,7 +2890,7 @@
       <c r="M84" s="16"/>
       <c r="N84" s="17"/>
     </row>
-    <row r="85" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A85" s="13"/>
       <c r="B85" s="14"/>
       <c r="C85" s="14"/>
@@ -2756,11 +2900,11 @@
       <c r="G85" s="14"/>
       <c r="H85" s="14"/>
       <c r="I85" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J85" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K85" s="16"/>
@@ -2768,7 +2912,7 @@
       <c r="M85" s="16"/>
       <c r="N85" s="17"/>
     </row>
-    <row r="86" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A86" s="13"/>
       <c r="B86" s="14"/>
       <c r="C86" s="14"/>
@@ -2778,11 +2922,11 @@
       <c r="G86" s="14"/>
       <c r="H86" s="14"/>
       <c r="I86" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J86" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K86" s="16"/>
@@ -2790,7 +2934,7 @@
       <c r="M86" s="16"/>
       <c r="N86" s="17"/>
     </row>
-    <row r="87" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A87" s="13"/>
       <c r="B87" s="14"/>
       <c r="C87" s="14"/>
@@ -2800,11 +2944,11 @@
       <c r="G87" s="14"/>
       <c r="H87" s="14"/>
       <c r="I87" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J87" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K87" s="16"/>
@@ -2812,7 +2956,7 @@
       <c r="M87" s="16"/>
       <c r="N87" s="17"/>
     </row>
-    <row r="88" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A88" s="13"/>
       <c r="B88" s="14"/>
       <c r="C88" s="14"/>
@@ -2822,11 +2966,11 @@
       <c r="G88" s="14"/>
       <c r="H88" s="14"/>
       <c r="I88" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J88" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K88" s="16"/>
@@ -2834,7 +2978,7 @@
       <c r="M88" s="16"/>
       <c r="N88" s="17"/>
     </row>
-    <row r="89" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A89" s="13"/>
       <c r="B89" s="14"/>
       <c r="C89" s="14"/>
@@ -2844,11 +2988,11 @@
       <c r="G89" s="14"/>
       <c r="H89" s="14"/>
       <c r="I89" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J89" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K89" s="16"/>
@@ -2856,7 +3000,7 @@
       <c r="M89" s="16"/>
       <c r="N89" s="17"/>
     </row>
-    <row r="90" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A90" s="13"/>
       <c r="B90" s="14"/>
       <c r="C90" s="14"/>
@@ -2866,11 +3010,11 @@
       <c r="G90" s="14"/>
       <c r="H90" s="14"/>
       <c r="I90" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J90" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K90" s="16"/>
@@ -2878,7 +3022,7 @@
       <c r="M90" s="16"/>
       <c r="N90" s="17"/>
     </row>
-    <row r="91" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A91" s="13"/>
       <c r="B91" s="14"/>
       <c r="C91" s="14"/>
@@ -2888,11 +3032,11 @@
       <c r="G91" s="14"/>
       <c r="H91" s="14"/>
       <c r="I91" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J91" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K91" s="16"/>
@@ -2900,7 +3044,7 @@
       <c r="M91" s="16"/>
       <c r="N91" s="17"/>
     </row>
-    <row r="92" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A92" s="13"/>
       <c r="B92" s="14"/>
       <c r="C92" s="14"/>
@@ -2910,11 +3054,11 @@
       <c r="G92" s="14"/>
       <c r="H92" s="14"/>
       <c r="I92" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J92" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K92" s="16"/>
@@ -2922,7 +3066,7 @@
       <c r="M92" s="16"/>
       <c r="N92" s="17"/>
     </row>
-    <row r="93" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A93" s="13"/>
       <c r="B93" s="14"/>
       <c r="C93" s="14"/>
@@ -2932,11 +3076,11 @@
       <c r="G93" s="14"/>
       <c r="H93" s="14"/>
       <c r="I93" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J93" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K93" s="16"/>
@@ -2944,7 +3088,7 @@
       <c r="M93" s="16"/>
       <c r="N93" s="17"/>
     </row>
-    <row r="94" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A94" s="13"/>
       <c r="B94" s="14"/>
       <c r="C94" s="14"/>
@@ -2954,11 +3098,11 @@
       <c r="G94" s="14"/>
       <c r="H94" s="14"/>
       <c r="I94" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J94" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K94" s="16"/>
@@ -2966,7 +3110,7 @@
       <c r="M94" s="16"/>
       <c r="N94" s="17"/>
     </row>
-    <row r="95" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A95" s="13"/>
       <c r="B95" s="14"/>
       <c r="C95" s="14"/>
@@ -2976,11 +3120,11 @@
       <c r="G95" s="14"/>
       <c r="H95" s="14"/>
       <c r="I95" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J95" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K95" s="16"/>
@@ -2988,7 +3132,7 @@
       <c r="M95" s="16"/>
       <c r="N95" s="17"/>
     </row>
-    <row r="96" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A96" s="13"/>
       <c r="B96" s="14"/>
       <c r="C96" s="14"/>
@@ -2998,11 +3142,11 @@
       <c r="G96" s="14"/>
       <c r="H96" s="14"/>
       <c r="I96" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J96" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K96" s="16"/>
@@ -3010,7 +3154,7 @@
       <c r="M96" s="16"/>
       <c r="N96" s="17"/>
     </row>
-    <row r="97" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A97" s="13"/>
       <c r="B97" s="14"/>
       <c r="C97" s="14"/>
@@ -3020,11 +3164,11 @@
       <c r="G97" s="14"/>
       <c r="H97" s="14"/>
       <c r="I97" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J97" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K97" s="16"/>
@@ -3032,7 +3176,7 @@
       <c r="M97" s="16"/>
       <c r="N97" s="17"/>
     </row>
-    <row r="98" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A98" s="13"/>
       <c r="B98" s="14"/>
       <c r="C98" s="14"/>
@@ -3042,11 +3186,11 @@
       <c r="G98" s="14"/>
       <c r="H98" s="14"/>
       <c r="I98" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J98" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K98" s="16"/>
@@ -3054,7 +3198,7 @@
       <c r="M98" s="16"/>
       <c r="N98" s="17"/>
     </row>
-    <row r="99" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A99" s="13"/>
       <c r="B99" s="14"/>
       <c r="C99" s="14"/>
@@ -3064,11 +3208,11 @@
       <c r="G99" s="14"/>
       <c r="H99" s="14"/>
       <c r="I99" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J99" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K99" s="16"/>
@@ -3076,7 +3220,7 @@
       <c r="M99" s="16"/>
       <c r="N99" s="17"/>
     </row>
-    <row r="100" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A100" s="13"/>
       <c r="B100" s="14"/>
       <c r="C100" s="14"/>
@@ -3086,11 +3230,11 @@
       <c r="G100" s="14"/>
       <c r="H100" s="14"/>
       <c r="I100" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J100" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K100" s="16"/>
@@ -3098,7 +3242,7 @@
       <c r="M100" s="16"/>
       <c r="N100" s="17"/>
     </row>
-    <row r="101" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A101" s="13"/>
       <c r="B101" s="14"/>
       <c r="C101" s="14"/>
@@ -3108,11 +3252,11 @@
       <c r="G101" s="14"/>
       <c r="H101" s="14"/>
       <c r="I101" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J101" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K101" s="16"/>
@@ -3120,7 +3264,7 @@
       <c r="M101" s="16"/>
       <c r="N101" s="17"/>
     </row>
-    <row r="102" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A102" s="13"/>
       <c r="B102" s="14"/>
       <c r="C102" s="14"/>
@@ -3130,11 +3274,11 @@
       <c r="G102" s="14"/>
       <c r="H102" s="14"/>
       <c r="I102" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J102" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K102" s="16"/>
@@ -3142,7 +3286,7 @@
       <c r="M102" s="16"/>
       <c r="N102" s="17"/>
     </row>
-    <row r="103" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A103" s="13"/>
       <c r="B103" s="14"/>
       <c r="C103" s="14"/>
@@ -3152,11 +3296,11 @@
       <c r="G103" s="14"/>
       <c r="H103" s="14"/>
       <c r="I103" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J103" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K103" s="16"/>
@@ -3164,7 +3308,7 @@
       <c r="M103" s="16"/>
       <c r="N103" s="17"/>
     </row>
-    <row r="104" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A104" s="13"/>
       <c r="B104" s="14"/>
       <c r="C104" s="14"/>
@@ -3174,11 +3318,11 @@
       <c r="G104" s="14"/>
       <c r="H104" s="14"/>
       <c r="I104" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J104" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K104" s="16"/>
@@ -3186,7 +3330,7 @@
       <c r="M104" s="16"/>
       <c r="N104" s="17"/>
     </row>
-    <row r="105" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A105" s="13"/>
       <c r="B105" s="14"/>
       <c r="C105" s="14"/>
@@ -3196,11 +3340,11 @@
       <c r="G105" s="14"/>
       <c r="H105" s="14"/>
       <c r="I105" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J105" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K105" s="16"/>
@@ -3208,7 +3352,7 @@
       <c r="M105" s="16"/>
       <c r="N105" s="17"/>
     </row>
-    <row r="106" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A106" s="13"/>
       <c r="B106" s="14"/>
       <c r="C106" s="14"/>
@@ -3218,11 +3362,11 @@
       <c r="G106" s="14"/>
       <c r="H106" s="14"/>
       <c r="I106" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J106" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K106" s="16"/>
@@ -3230,7 +3374,7 @@
       <c r="M106" s="16"/>
       <c r="N106" s="17"/>
     </row>
-    <row r="107" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A107" s="13"/>
       <c r="B107" s="14"/>
       <c r="C107" s="14"/>
@@ -3240,11 +3384,11 @@
       <c r="G107" s="14"/>
       <c r="H107" s="14"/>
       <c r="I107" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J107" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K107" s="16"/>
@@ -3252,7 +3396,7 @@
       <c r="M107" s="16"/>
       <c r="N107" s="17"/>
     </row>
-    <row r="108" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A108" s="13"/>
       <c r="B108" s="14"/>
       <c r="C108" s="14"/>
@@ -3262,11 +3406,11 @@
       <c r="G108" s="14"/>
       <c r="H108" s="14"/>
       <c r="I108" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J108" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K108" s="16"/>
@@ -3274,7 +3418,7 @@
       <c r="M108" s="16"/>
       <c r="N108" s="17"/>
     </row>
-    <row r="109" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A109" s="13"/>
       <c r="B109" s="14"/>
       <c r="C109" s="14"/>
@@ -3284,11 +3428,11 @@
       <c r="G109" s="14"/>
       <c r="H109" s="14"/>
       <c r="I109" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J109" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K109" s="16"/>
@@ -3296,7 +3440,7 @@
       <c r="M109" s="16"/>
       <c r="N109" s="17"/>
     </row>
-    <row r="110" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A110" s="13"/>
       <c r="B110" s="14"/>
       <c r="C110" s="14"/>
@@ -3306,11 +3450,11 @@
       <c r="G110" s="14"/>
       <c r="H110" s="14"/>
       <c r="I110" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J110" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K110" s="16"/>
@@ -3318,7 +3462,7 @@
       <c r="M110" s="16"/>
       <c r="N110" s="17"/>
     </row>
-    <row r="111" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A111" s="13"/>
       <c r="B111" s="14"/>
       <c r="C111" s="14"/>
@@ -3328,11 +3472,11 @@
       <c r="G111" s="14"/>
       <c r="H111" s="14"/>
       <c r="I111" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J111" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K111" s="16"/>
@@ -3340,7 +3484,7 @@
       <c r="M111" s="16"/>
       <c r="N111" s="17"/>
     </row>
-    <row r="112" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A112" s="13"/>
       <c r="B112" s="14"/>
       <c r="C112" s="14"/>
@@ -3350,11 +3494,11 @@
       <c r="G112" s="14"/>
       <c r="H112" s="14"/>
       <c r="I112" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J112" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K112" s="16"/>
@@ -3362,7 +3506,7 @@
       <c r="M112" s="16"/>
       <c r="N112" s="17"/>
     </row>
-    <row r="113" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A113" s="13"/>
       <c r="B113" s="14"/>
       <c r="C113" s="14"/>
@@ -3372,11 +3516,11 @@
       <c r="G113" s="14"/>
       <c r="H113" s="14"/>
       <c r="I113" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J113" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K113" s="16"/>
@@ -3384,7 +3528,7 @@
       <c r="M113" s="16"/>
       <c r="N113" s="17"/>
     </row>
-    <row r="114" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A114" s="13"/>
       <c r="B114" s="14"/>
       <c r="C114" s="14"/>
@@ -3394,11 +3538,11 @@
       <c r="G114" s="14"/>
       <c r="H114" s="14"/>
       <c r="I114" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J114" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K114" s="16"/>
@@ -3406,7 +3550,7 @@
       <c r="M114" s="16"/>
       <c r="N114" s="17"/>
     </row>
-    <row r="115" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A115" s="13"/>
       <c r="B115" s="14"/>
       <c r="C115" s="14"/>
@@ -3416,11 +3560,11 @@
       <c r="G115" s="14"/>
       <c r="H115" s="14"/>
       <c r="I115" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J115" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K115" s="16"/>
@@ -3428,7 +3572,7 @@
       <c r="M115" s="16"/>
       <c r="N115" s="17"/>
     </row>
-    <row r="116" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A116" s="13"/>
       <c r="B116" s="14"/>
       <c r="C116" s="14"/>
@@ -3438,11 +3582,11 @@
       <c r="G116" s="14"/>
       <c r="H116" s="14"/>
       <c r="I116" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J116" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K116" s="16"/>
@@ -3450,7 +3594,7 @@
       <c r="M116" s="16"/>
       <c r="N116" s="17"/>
     </row>
-    <row r="117" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A117" s="13"/>
       <c r="B117" s="14"/>
       <c r="C117" s="14"/>
@@ -3460,11 +3604,11 @@
       <c r="G117" s="14"/>
       <c r="H117" s="14"/>
       <c r="I117" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J117" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K117" s="16"/>
@@ -3472,7 +3616,7 @@
       <c r="M117" s="16"/>
       <c r="N117" s="17"/>
     </row>
-    <row r="118" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A118" s="13"/>
       <c r="B118" s="14"/>
       <c r="C118" s="14"/>
@@ -3482,11 +3626,11 @@
       <c r="G118" s="14"/>
       <c r="H118" s="14"/>
       <c r="I118" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J118" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K118" s="16"/>
@@ -3494,7 +3638,7 @@
       <c r="M118" s="16"/>
       <c r="N118" s="17"/>
     </row>
-    <row r="119" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A119" s="13"/>
       <c r="B119" s="14"/>
       <c r="C119" s="14"/>
@@ -3504,11 +3648,11 @@
       <c r="G119" s="14"/>
       <c r="H119" s="14"/>
       <c r="I119" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J119" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K119" s="16"/>
@@ -3516,7 +3660,7 @@
       <c r="M119" s="16"/>
       <c r="N119" s="17"/>
     </row>
-    <row r="120" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A120" s="13"/>
       <c r="B120" s="14"/>
       <c r="C120" s="14"/>
@@ -3526,11 +3670,11 @@
       <c r="G120" s="14"/>
       <c r="H120" s="14"/>
       <c r="I120" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J120" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K120" s="16"/>
@@ -3538,7 +3682,7 @@
       <c r="M120" s="16"/>
       <c r="N120" s="17"/>
     </row>
-    <row r="121" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A121" s="13"/>
       <c r="B121" s="14"/>
       <c r="C121" s="14"/>
@@ -3548,11 +3692,11 @@
       <c r="G121" s="14"/>
       <c r="H121" s="14"/>
       <c r="I121" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J121" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K121" s="16"/>
@@ -3560,7 +3704,7 @@
       <c r="M121" s="16"/>
       <c r="N121" s="17"/>
     </row>
-    <row r="122" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A122" s="13"/>
       <c r="B122" s="14"/>
       <c r="C122" s="14"/>
@@ -3570,11 +3714,11 @@
       <c r="G122" s="14"/>
       <c r="H122" s="14"/>
       <c r="I122" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J122" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K122" s="16"/>
@@ -3582,7 +3726,7 @@
       <c r="M122" s="16"/>
       <c r="N122" s="17"/>
     </row>
-    <row r="123" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A123" s="13"/>
       <c r="B123" s="14"/>
       <c r="C123" s="14"/>
@@ -3592,11 +3736,11 @@
       <c r="G123" s="14"/>
       <c r="H123" s="14"/>
       <c r="I123" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J123" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K123" s="16"/>
@@ -3604,7 +3748,7 @@
       <c r="M123" s="16"/>
       <c r="N123" s="17"/>
     </row>
-    <row r="124" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A124" s="13"/>
       <c r="B124" s="14"/>
       <c r="C124" s="14"/>
@@ -3614,11 +3758,11 @@
       <c r="G124" s="14"/>
       <c r="H124" s="14"/>
       <c r="I124" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J124" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K124" s="16"/>
@@ -3626,7 +3770,7 @@
       <c r="M124" s="16"/>
       <c r="N124" s="17"/>
     </row>
-    <row r="125" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A125" s="13"/>
       <c r="B125" s="14"/>
       <c r="C125" s="14"/>
@@ -3636,11 +3780,11 @@
       <c r="G125" s="14"/>
       <c r="H125" s="14"/>
       <c r="I125" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J125" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K125" s="16"/>
@@ -3648,7 +3792,7 @@
       <c r="M125" s="16"/>
       <c r="N125" s="17"/>
     </row>
-    <row r="126" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A126" s="13"/>
       <c r="B126" s="14"/>
       <c r="C126" s="14"/>
@@ -3658,11 +3802,11 @@
       <c r="G126" s="14"/>
       <c r="H126" s="14"/>
       <c r="I126" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J126" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K126" s="16"/>
@@ -3670,7 +3814,7 @@
       <c r="M126" s="16"/>
       <c r="N126" s="17"/>
     </row>
-    <row r="127" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A127" s="13"/>
       <c r="B127" s="14"/>
       <c r="C127" s="14"/>
@@ -3680,11 +3824,11 @@
       <c r="G127" s="14"/>
       <c r="H127" s="14"/>
       <c r="I127" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J127" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K127" s="16"/>
@@ -3692,7 +3836,7 @@
       <c r="M127" s="16"/>
       <c r="N127" s="17"/>
     </row>
-    <row r="128" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A128" s="13"/>
       <c r="B128" s="14"/>
       <c r="C128" s="14"/>
@@ -3702,11 +3846,11 @@
       <c r="G128" s="14"/>
       <c r="H128" s="14"/>
       <c r="I128" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J128" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K128" s="16"/>
@@ -3714,7 +3858,7 @@
       <c r="M128" s="16"/>
       <c r="N128" s="17"/>
     </row>
-    <row r="129" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A129" s="13"/>
       <c r="B129" s="14"/>
       <c r="C129" s="14"/>
@@ -3724,11 +3868,11 @@
       <c r="G129" s="14"/>
       <c r="H129" s="14"/>
       <c r="I129" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J129" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K129" s="16"/>
@@ -3736,7 +3880,7 @@
       <c r="M129" s="16"/>
       <c r="N129" s="17"/>
     </row>
-    <row r="130" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A130" s="13"/>
       <c r="B130" s="14"/>
       <c r="C130" s="14"/>
@@ -3746,11 +3890,11 @@
       <c r="G130" s="14"/>
       <c r="H130" s="14"/>
       <c r="I130" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J130" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K130" s="16"/>
@@ -3758,7 +3902,7 @@
       <c r="M130" s="16"/>
       <c r="N130" s="17"/>
     </row>
-    <row r="131" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A131" s="13"/>
       <c r="B131" s="14"/>
       <c r="C131" s="14"/>
@@ -3768,11 +3912,11 @@
       <c r="G131" s="14"/>
       <c r="H131" s="14"/>
       <c r="I131" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J131" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K131" s="16"/>
@@ -3780,7 +3924,7 @@
       <c r="M131" s="16"/>
       <c r="N131" s="17"/>
     </row>
-    <row r="132" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A132" s="13"/>
       <c r="B132" s="14"/>
       <c r="C132" s="14"/>
@@ -3790,11 +3934,11 @@
       <c r="G132" s="14"/>
       <c r="H132" s="14"/>
       <c r="I132" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J132" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K132" s="16"/>
@@ -3802,7 +3946,7 @@
       <c r="M132" s="16"/>
       <c r="N132" s="17"/>
     </row>
-    <row r="133" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A133" s="13"/>
       <c r="B133" s="14"/>
       <c r="C133" s="14"/>
@@ -3812,11 +3956,11 @@
       <c r="G133" s="14"/>
       <c r="H133" s="14"/>
       <c r="I133" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J133" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K133" s="16"/>
@@ -3824,7 +3968,7 @@
       <c r="M133" s="16"/>
       <c r="N133" s="17"/>
     </row>
-    <row r="134" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A134" s="13"/>
       <c r="B134" s="14"/>
       <c r="C134" s="14"/>
@@ -3834,11 +3978,11 @@
       <c r="G134" s="14"/>
       <c r="H134" s="14"/>
       <c r="I134" s="15" t="str">
-        <f t="shared" ref="I134:I197" si="4">IF(SUM(B134:F134,H134)=0,"",SUM(B134:F134,H134))</f>
+        <f t="shared" ref="I134:I197" si="6">IF(SUM(B134:F134,H134)=0,"",SUM(B134:F134,H134))</f>
         <v/>
       </c>
       <c r="J134" s="15" t="str">
-        <f t="shared" ref="J134:J197" si="5">IF(I134="","",1440-I134)</f>
+        <f t="shared" ref="J134:J197" si="7">IF(I134="","",1440-I134)</f>
         <v/>
       </c>
       <c r="K134" s="16"/>
@@ -3846,7 +3990,7 @@
       <c r="M134" s="16"/>
       <c r="N134" s="17"/>
     </row>
-    <row r="135" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A135" s="13"/>
       <c r="B135" s="14"/>
       <c r="C135" s="14"/>
@@ -3856,11 +4000,11 @@
       <c r="G135" s="14"/>
       <c r="H135" s="14"/>
       <c r="I135" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J135" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K135" s="16"/>
@@ -3868,7 +4012,7 @@
       <c r="M135" s="16"/>
       <c r="N135" s="17"/>
     </row>
-    <row r="136" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A136" s="13"/>
       <c r="B136" s="14"/>
       <c r="C136" s="14"/>
@@ -3878,11 +4022,11 @@
       <c r="G136" s="14"/>
       <c r="H136" s="14"/>
       <c r="I136" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J136" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K136" s="16"/>
@@ -3890,7 +4034,7 @@
       <c r="M136" s="16"/>
       <c r="N136" s="17"/>
     </row>
-    <row r="137" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A137" s="13"/>
       <c r="B137" s="14"/>
       <c r="C137" s="14"/>
@@ -3900,11 +4044,11 @@
       <c r="G137" s="14"/>
       <c r="H137" s="14"/>
       <c r="I137" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J137" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K137" s="16"/>
@@ -3912,7 +4056,7 @@
       <c r="M137" s="16"/>
       <c r="N137" s="17"/>
     </row>
-    <row r="138" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A138" s="13"/>
       <c r="B138" s="14"/>
       <c r="C138" s="14"/>
@@ -3922,11 +4066,11 @@
       <c r="G138" s="14"/>
       <c r="H138" s="14"/>
       <c r="I138" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J138" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K138" s="16"/>
@@ -3934,7 +4078,7 @@
       <c r="M138" s="16"/>
       <c r="N138" s="17"/>
     </row>
-    <row r="139" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A139" s="13"/>
       <c r="B139" s="14"/>
       <c r="C139" s="14"/>
@@ -3944,11 +4088,11 @@
       <c r="G139" s="14"/>
       <c r="H139" s="14"/>
       <c r="I139" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J139" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K139" s="16"/>
@@ -3956,7 +4100,7 @@
       <c r="M139" s="16"/>
       <c r="N139" s="17"/>
     </row>
-    <row r="140" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A140" s="13"/>
       <c r="B140" s="14"/>
       <c r="C140" s="14"/>
@@ -3966,11 +4110,11 @@
       <c r="G140" s="14"/>
       <c r="H140" s="14"/>
       <c r="I140" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J140" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K140" s="16"/>
@@ -3978,7 +4122,7 @@
       <c r="M140" s="16"/>
       <c r="N140" s="17"/>
     </row>
-    <row r="141" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A141" s="13"/>
       <c r="B141" s="14"/>
       <c r="C141" s="14"/>
@@ -3988,11 +4132,11 @@
       <c r="G141" s="14"/>
       <c r="H141" s="14"/>
       <c r="I141" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J141" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K141" s="16"/>
@@ -4000,7 +4144,7 @@
       <c r="M141" s="16"/>
       <c r="N141" s="17"/>
     </row>
-    <row r="142" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A142" s="13"/>
       <c r="B142" s="14"/>
       <c r="C142" s="14"/>
@@ -4010,11 +4154,11 @@
       <c r="G142" s="14"/>
       <c r="H142" s="14"/>
       <c r="I142" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J142" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K142" s="16"/>
@@ -4022,7 +4166,7 @@
       <c r="M142" s="16"/>
       <c r="N142" s="17"/>
     </row>
-    <row r="143" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A143" s="13"/>
       <c r="B143" s="14"/>
       <c r="C143" s="14"/>
@@ -4032,11 +4176,11 @@
       <c r="G143" s="14"/>
       <c r="H143" s="14"/>
       <c r="I143" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J143" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K143" s="16"/>
@@ -4044,7 +4188,7 @@
       <c r="M143" s="16"/>
       <c r="N143" s="17"/>
     </row>
-    <row r="144" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A144" s="13"/>
       <c r="B144" s="14"/>
       <c r="C144" s="14"/>
@@ -4054,11 +4198,11 @@
       <c r="G144" s="14"/>
       <c r="H144" s="14"/>
       <c r="I144" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J144" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K144" s="16"/>
@@ -4066,7 +4210,7 @@
       <c r="M144" s="16"/>
       <c r="N144" s="17"/>
     </row>
-    <row r="145" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A145" s="13"/>
       <c r="B145" s="14"/>
       <c r="C145" s="14"/>
@@ -4076,11 +4220,11 @@
       <c r="G145" s="14"/>
       <c r="H145" s="14"/>
       <c r="I145" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J145" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K145" s="16"/>
@@ -4088,7 +4232,7 @@
       <c r="M145" s="16"/>
       <c r="N145" s="17"/>
     </row>
-    <row r="146" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A146" s="13"/>
       <c r="B146" s="14"/>
       <c r="C146" s="14"/>
@@ -4098,11 +4242,11 @@
       <c r="G146" s="14"/>
       <c r="H146" s="14"/>
       <c r="I146" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J146" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K146" s="16"/>
@@ -4110,7 +4254,7 @@
       <c r="M146" s="16"/>
       <c r="N146" s="17"/>
     </row>
-    <row r="147" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A147" s="13"/>
       <c r="B147" s="14"/>
       <c r="C147" s="14"/>
@@ -4120,11 +4264,11 @@
       <c r="G147" s="14"/>
       <c r="H147" s="14"/>
       <c r="I147" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J147" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K147" s="16"/>
@@ -4132,7 +4276,7 @@
       <c r="M147" s="16"/>
       <c r="N147" s="17"/>
     </row>
-    <row r="148" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A148" s="13"/>
       <c r="B148" s="14"/>
       <c r="C148" s="14"/>
@@ -4142,11 +4286,11 @@
       <c r="G148" s="14"/>
       <c r="H148" s="14"/>
       <c r="I148" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J148" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K148" s="16"/>
@@ -4154,7 +4298,7 @@
       <c r="M148" s="16"/>
       <c r="N148" s="17"/>
     </row>
-    <row r="149" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A149" s="13"/>
       <c r="B149" s="14"/>
       <c r="C149" s="14"/>
@@ -4164,11 +4308,11 @@
       <c r="G149" s="14"/>
       <c r="H149" s="14"/>
       <c r="I149" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J149" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K149" s="16"/>
@@ -4176,7 +4320,7 @@
       <c r="M149" s="16"/>
       <c r="N149" s="17"/>
     </row>
-    <row r="150" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A150" s="13"/>
       <c r="B150" s="14"/>
       <c r="C150" s="14"/>
@@ -4186,11 +4330,11 @@
       <c r="G150" s="14"/>
       <c r="H150" s="14"/>
       <c r="I150" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J150" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K150" s="16"/>
@@ -4198,7 +4342,7 @@
       <c r="M150" s="16"/>
       <c r="N150" s="17"/>
     </row>
-    <row r="151" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A151" s="13"/>
       <c r="B151" s="14"/>
       <c r="C151" s="14"/>
@@ -4208,11 +4352,11 @@
       <c r="G151" s="14"/>
       <c r="H151" s="14"/>
       <c r="I151" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J151" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K151" s="16"/>
@@ -4220,7 +4364,7 @@
       <c r="M151" s="16"/>
       <c r="N151" s="17"/>
     </row>
-    <row r="152" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A152" s="13"/>
       <c r="B152" s="14"/>
       <c r="C152" s="14"/>
@@ -4230,11 +4374,11 @@
       <c r="G152" s="14"/>
       <c r="H152" s="14"/>
       <c r="I152" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J152" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K152" s="16"/>
@@ -4242,7 +4386,7 @@
       <c r="M152" s="16"/>
       <c r="N152" s="17"/>
     </row>
-    <row r="153" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A153" s="13"/>
       <c r="B153" s="14"/>
       <c r="C153" s="14"/>
@@ -4252,11 +4396,11 @@
       <c r="G153" s="14"/>
       <c r="H153" s="14"/>
       <c r="I153" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J153" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K153" s="16"/>
@@ -4264,7 +4408,7 @@
       <c r="M153" s="16"/>
       <c r="N153" s="17"/>
     </row>
-    <row r="154" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A154" s="13"/>
       <c r="B154" s="14"/>
       <c r="C154" s="14"/>
@@ -4274,11 +4418,11 @@
       <c r="G154" s="14"/>
       <c r="H154" s="14"/>
       <c r="I154" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J154" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K154" s="16"/>
@@ -4286,7 +4430,7 @@
       <c r="M154" s="16"/>
       <c r="N154" s="17"/>
     </row>
-    <row r="155" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A155" s="13"/>
       <c r="B155" s="14"/>
       <c r="C155" s="14"/>
@@ -4296,11 +4440,11 @@
       <c r="G155" s="14"/>
       <c r="H155" s="14"/>
       <c r="I155" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J155" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K155" s="16"/>
@@ -4308,7 +4452,7 @@
       <c r="M155" s="16"/>
       <c r="N155" s="17"/>
     </row>
-    <row r="156" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A156" s="13"/>
       <c r="B156" s="14"/>
       <c r="C156" s="14"/>
@@ -4318,11 +4462,11 @@
       <c r="G156" s="14"/>
       <c r="H156" s="14"/>
       <c r="I156" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J156" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K156" s="16"/>
@@ -4330,7 +4474,7 @@
       <c r="M156" s="16"/>
       <c r="N156" s="17"/>
     </row>
-    <row r="157" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A157" s="13"/>
       <c r="B157" s="14"/>
       <c r="C157" s="14"/>
@@ -4340,11 +4484,11 @@
       <c r="G157" s="14"/>
       <c r="H157" s="14"/>
       <c r="I157" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J157" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K157" s="16"/>
@@ -4352,7 +4496,7 @@
       <c r="M157" s="16"/>
       <c r="N157" s="17"/>
     </row>
-    <row r="158" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A158" s="13"/>
       <c r="B158" s="14"/>
       <c r="C158" s="14"/>
@@ -4362,11 +4506,11 @@
       <c r="G158" s="14"/>
       <c r="H158" s="14"/>
       <c r="I158" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J158" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K158" s="16"/>
@@ -4374,7 +4518,7 @@
       <c r="M158" s="16"/>
       <c r="N158" s="17"/>
     </row>
-    <row r="159" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A159" s="13"/>
       <c r="B159" s="14"/>
       <c r="C159" s="14"/>
@@ -4384,11 +4528,11 @@
       <c r="G159" s="14"/>
       <c r="H159" s="14"/>
       <c r="I159" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J159" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K159" s="16"/>
@@ -4396,7 +4540,7 @@
       <c r="M159" s="16"/>
       <c r="N159" s="17"/>
     </row>
-    <row r="160" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A160" s="13"/>
       <c r="B160" s="14"/>
       <c r="C160" s="14"/>
@@ -4406,11 +4550,11 @@
       <c r="G160" s="14"/>
       <c r="H160" s="14"/>
       <c r="I160" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J160" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K160" s="16"/>
@@ -4418,7 +4562,7 @@
       <c r="M160" s="16"/>
       <c r="N160" s="17"/>
     </row>
-    <row r="161" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A161" s="13"/>
       <c r="B161" s="14"/>
       <c r="C161" s="14"/>
@@ -4428,11 +4572,11 @@
       <c r="G161" s="14"/>
       <c r="H161" s="14"/>
       <c r="I161" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J161" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K161" s="16"/>
@@ -4440,7 +4584,7 @@
       <c r="M161" s="16"/>
       <c r="N161" s="17"/>
     </row>
-    <row r="162" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A162" s="13"/>
       <c r="B162" s="14"/>
       <c r="C162" s="14"/>
@@ -4450,11 +4594,11 @@
       <c r="G162" s="14"/>
       <c r="H162" s="14"/>
       <c r="I162" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J162" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K162" s="16"/>
@@ -4462,7 +4606,7 @@
       <c r="M162" s="16"/>
       <c r="N162" s="17"/>
     </row>
-    <row r="163" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A163" s="13"/>
       <c r="B163" s="14"/>
       <c r="C163" s="14"/>
@@ -4472,11 +4616,11 @@
       <c r="G163" s="14"/>
       <c r="H163" s="14"/>
       <c r="I163" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J163" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K163" s="16"/>
@@ -4484,7 +4628,7 @@
       <c r="M163" s="16"/>
       <c r="N163" s="17"/>
     </row>
-    <row r="164" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A164" s="13"/>
       <c r="B164" s="14"/>
       <c r="C164" s="14"/>
@@ -4494,11 +4638,11 @@
       <c r="G164" s="14"/>
       <c r="H164" s="14"/>
       <c r="I164" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J164" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K164" s="16"/>
@@ -4506,7 +4650,7 @@
       <c r="M164" s="16"/>
       <c r="N164" s="17"/>
     </row>
-    <row r="165" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A165" s="13"/>
       <c r="B165" s="14"/>
       <c r="C165" s="14"/>
@@ -4516,11 +4660,11 @@
       <c r="G165" s="14"/>
       <c r="H165" s="14"/>
       <c r="I165" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J165" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K165" s="16"/>
@@ -4528,7 +4672,7 @@
       <c r="M165" s="16"/>
       <c r="N165" s="17"/>
     </row>
-    <row r="166" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A166" s="13"/>
       <c r="B166" s="14"/>
       <c r="C166" s="14"/>
@@ -4538,11 +4682,11 @@
       <c r="G166" s="14"/>
       <c r="H166" s="14"/>
       <c r="I166" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J166" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K166" s="16"/>
@@ -4550,7 +4694,7 @@
       <c r="M166" s="16"/>
       <c r="N166" s="17"/>
     </row>
-    <row r="167" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A167" s="13"/>
       <c r="B167" s="14"/>
       <c r="C167" s="14"/>
@@ -4560,11 +4704,11 @@
       <c r="G167" s="14"/>
       <c r="H167" s="14"/>
       <c r="I167" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J167" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K167" s="16"/>
@@ -4572,7 +4716,7 @@
       <c r="M167" s="16"/>
       <c r="N167" s="17"/>
     </row>
-    <row r="168" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A168" s="13"/>
       <c r="B168" s="14"/>
       <c r="C168" s="14"/>
@@ -4582,11 +4726,11 @@
       <c r="G168" s="14"/>
       <c r="H168" s="14"/>
       <c r="I168" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J168" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K168" s="16"/>
@@ -4594,7 +4738,7 @@
       <c r="M168" s="16"/>
       <c r="N168" s="17"/>
     </row>
-    <row r="169" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A169" s="13"/>
       <c r="B169" s="14"/>
       <c r="C169" s="14"/>
@@ -4604,11 +4748,11 @@
       <c r="G169" s="14"/>
       <c r="H169" s="14"/>
       <c r="I169" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J169" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K169" s="16"/>
@@ -4616,7 +4760,7 @@
       <c r="M169" s="16"/>
       <c r="N169" s="17"/>
     </row>
-    <row r="170" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A170" s="13"/>
       <c r="B170" s="14"/>
       <c r="C170" s="14"/>
@@ -4626,11 +4770,11 @@
       <c r="G170" s="14"/>
       <c r="H170" s="14"/>
       <c r="I170" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J170" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K170" s="16"/>
@@ -4638,7 +4782,7 @@
       <c r="M170" s="16"/>
       <c r="N170" s="17"/>
     </row>
-    <row r="171" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A171" s="13"/>
       <c r="B171" s="14"/>
       <c r="C171" s="14"/>
@@ -4648,11 +4792,11 @@
       <c r="G171" s="14"/>
       <c r="H171" s="14"/>
       <c r="I171" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J171" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K171" s="16"/>
@@ -4660,7 +4804,7 @@
       <c r="M171" s="16"/>
       <c r="N171" s="17"/>
     </row>
-    <row r="172" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A172" s="13"/>
       <c r="B172" s="14"/>
       <c r="C172" s="14"/>
@@ -4670,11 +4814,11 @@
       <c r="G172" s="14"/>
       <c r="H172" s="14"/>
       <c r="I172" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J172" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K172" s="16"/>
@@ -4682,7 +4826,7 @@
       <c r="M172" s="16"/>
       <c r="N172" s="17"/>
     </row>
-    <row r="173" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A173" s="13"/>
       <c r="B173" s="14"/>
       <c r="C173" s="14"/>
@@ -4692,11 +4836,11 @@
       <c r="G173" s="14"/>
       <c r="H173" s="14"/>
       <c r="I173" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J173" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K173" s="16"/>
@@ -4704,7 +4848,7 @@
       <c r="M173" s="16"/>
       <c r="N173" s="17"/>
     </row>
-    <row r="174" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A174" s="13"/>
       <c r="B174" s="14"/>
       <c r="C174" s="14"/>
@@ -4714,11 +4858,11 @@
       <c r="G174" s="14"/>
       <c r="H174" s="14"/>
       <c r="I174" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J174" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K174" s="16"/>
@@ -4726,7 +4870,7 @@
       <c r="M174" s="16"/>
       <c r="N174" s="17"/>
     </row>
-    <row r="175" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A175" s="13"/>
       <c r="B175" s="14"/>
       <c r="C175" s="14"/>
@@ -4736,11 +4880,11 @@
       <c r="G175" s="14"/>
       <c r="H175" s="14"/>
       <c r="I175" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J175" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K175" s="16"/>
@@ -4748,7 +4892,7 @@
       <c r="M175" s="16"/>
       <c r="N175" s="17"/>
     </row>
-    <row r="176" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A176" s="13"/>
       <c r="B176" s="14"/>
       <c r="C176" s="14"/>
@@ -4758,11 +4902,11 @@
       <c r="G176" s="14"/>
       <c r="H176" s="14"/>
       <c r="I176" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J176" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K176" s="16"/>
@@ -4770,7 +4914,7 @@
       <c r="M176" s="16"/>
       <c r="N176" s="17"/>
     </row>
-    <row r="177" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A177" s="13"/>
       <c r="B177" s="14"/>
       <c r="C177" s="14"/>
@@ -4780,11 +4924,11 @@
       <c r="G177" s="14"/>
       <c r="H177" s="14"/>
       <c r="I177" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J177" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K177" s="16"/>
@@ -4792,7 +4936,7 @@
       <c r="M177" s="16"/>
       <c r="N177" s="17"/>
     </row>
-    <row r="178" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A178" s="13"/>
       <c r="B178" s="14"/>
       <c r="C178" s="14"/>
@@ -4802,11 +4946,11 @@
       <c r="G178" s="14"/>
       <c r="H178" s="14"/>
       <c r="I178" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J178" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K178" s="16"/>
@@ -4814,7 +4958,7 @@
       <c r="M178" s="16"/>
       <c r="N178" s="17"/>
     </row>
-    <row r="179" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A179" s="13"/>
       <c r="B179" s="14"/>
       <c r="C179" s="14"/>
@@ -4824,11 +4968,11 @@
       <c r="G179" s="14"/>
       <c r="H179" s="14"/>
       <c r="I179" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J179" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K179" s="16"/>
@@ -4836,7 +4980,7 @@
       <c r="M179" s="16"/>
       <c r="N179" s="17"/>
     </row>
-    <row r="180" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A180" s="13"/>
       <c r="B180" s="14"/>
       <c r="C180" s="14"/>
@@ -4846,11 +4990,11 @@
       <c r="G180" s="14"/>
       <c r="H180" s="14"/>
       <c r="I180" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J180" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K180" s="16"/>
@@ -4858,7 +5002,7 @@
       <c r="M180" s="16"/>
       <c r="N180" s="17"/>
     </row>
-    <row r="181" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A181" s="13"/>
       <c r="B181" s="14"/>
       <c r="C181" s="14"/>
@@ -4868,11 +5012,11 @@
       <c r="G181" s="14"/>
       <c r="H181" s="14"/>
       <c r="I181" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J181" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K181" s="16"/>
@@ -4880,7 +5024,7 @@
       <c r="M181" s="16"/>
       <c r="N181" s="17"/>
     </row>
-    <row r="182" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A182" s="13"/>
       <c r="B182" s="14"/>
       <c r="C182" s="14"/>
@@ -4890,11 +5034,11 @@
       <c r="G182" s="14"/>
       <c r="H182" s="14"/>
       <c r="I182" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J182" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K182" s="16"/>
@@ -4902,7 +5046,7 @@
       <c r="M182" s="16"/>
       <c r="N182" s="17"/>
     </row>
-    <row r="183" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A183" s="13"/>
       <c r="B183" s="14"/>
       <c r="C183" s="14"/>
@@ -4912,11 +5056,11 @@
       <c r="G183" s="14"/>
       <c r="H183" s="14"/>
       <c r="I183" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J183" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K183" s="16"/>
@@ -4924,7 +5068,7 @@
       <c r="M183" s="16"/>
       <c r="N183" s="17"/>
     </row>
-    <row r="184" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A184" s="13"/>
       <c r="B184" s="14"/>
       <c r="C184" s="14"/>
@@ -4934,11 +5078,11 @@
       <c r="G184" s="14"/>
       <c r="H184" s="14"/>
       <c r="I184" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J184" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K184" s="16"/>
@@ -4946,7 +5090,7 @@
       <c r="M184" s="16"/>
       <c r="N184" s="17"/>
     </row>
-    <row r="185" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A185" s="13"/>
       <c r="B185" s="14"/>
       <c r="C185" s="14"/>
@@ -4956,11 +5100,11 @@
       <c r="G185" s="14"/>
       <c r="H185" s="14"/>
       <c r="I185" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J185" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K185" s="16"/>
@@ -4968,7 +5112,7 @@
       <c r="M185" s="16"/>
       <c r="N185" s="17"/>
     </row>
-    <row r="186" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A186" s="13"/>
       <c r="B186" s="14"/>
       <c r="C186" s="14"/>
@@ -4978,11 +5122,11 @@
       <c r="G186" s="14"/>
       <c r="H186" s="14"/>
       <c r="I186" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J186" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K186" s="16"/>
@@ -4990,7 +5134,7 @@
       <c r="M186" s="16"/>
       <c r="N186" s="17"/>
     </row>
-    <row r="187" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A187" s="13"/>
       <c r="B187" s="14"/>
       <c r="C187" s="14"/>
@@ -5000,11 +5144,11 @@
       <c r="G187" s="14"/>
       <c r="H187" s="14"/>
       <c r="I187" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J187" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K187" s="16"/>
@@ -5012,7 +5156,7 @@
       <c r="M187" s="16"/>
       <c r="N187" s="17"/>
     </row>
-    <row r="188" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A188" s="13"/>
       <c r="B188" s="14"/>
       <c r="C188" s="14"/>
@@ -5022,11 +5166,11 @@
       <c r="G188" s="14"/>
       <c r="H188" s="14"/>
       <c r="I188" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J188" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K188" s="16"/>
@@ -5034,7 +5178,7 @@
       <c r="M188" s="16"/>
       <c r="N188" s="17"/>
     </row>
-    <row r="189" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A189" s="13"/>
       <c r="B189" s="14"/>
       <c r="C189" s="14"/>
@@ -5044,11 +5188,11 @@
       <c r="G189" s="14"/>
       <c r="H189" s="14"/>
       <c r="I189" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J189" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K189" s="16"/>
@@ -5056,7 +5200,7 @@
       <c r="M189" s="16"/>
       <c r="N189" s="17"/>
     </row>
-    <row r="190" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A190" s="13"/>
       <c r="B190" s="14"/>
       <c r="C190" s="14"/>
@@ -5066,11 +5210,11 @@
       <c r="G190" s="14"/>
       <c r="H190" s="14"/>
       <c r="I190" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J190" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K190" s="16"/>
@@ -5078,7 +5222,7 @@
       <c r="M190" s="16"/>
       <c r="N190" s="17"/>
     </row>
-    <row r="191" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A191" s="13"/>
       <c r="B191" s="14"/>
       <c r="C191" s="14"/>
@@ -5088,11 +5232,11 @@
       <c r="G191" s="14"/>
       <c r="H191" s="14"/>
       <c r="I191" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J191" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K191" s="16"/>
@@ -5100,7 +5244,7 @@
       <c r="M191" s="16"/>
       <c r="N191" s="17"/>
     </row>
-    <row r="192" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A192" s="13"/>
       <c r="B192" s="14"/>
       <c r="C192" s="14"/>
@@ -5110,11 +5254,11 @@
       <c r="G192" s="14"/>
       <c r="H192" s="14"/>
       <c r="I192" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J192" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K192" s="16"/>
@@ -5122,7 +5266,7 @@
       <c r="M192" s="16"/>
       <c r="N192" s="17"/>
     </row>
-    <row r="193" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A193" s="13"/>
       <c r="B193" s="14"/>
       <c r="C193" s="14"/>
@@ -5132,11 +5276,11 @@
       <c r="G193" s="14"/>
       <c r="H193" s="14"/>
       <c r="I193" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J193" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K193" s="16"/>
@@ -5144,7 +5288,7 @@
       <c r="M193" s="16"/>
       <c r="N193" s="17"/>
     </row>
-    <row r="194" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A194" s="13"/>
       <c r="B194" s="14"/>
       <c r="C194" s="14"/>
@@ -5154,11 +5298,11 @@
       <c r="G194" s="14"/>
       <c r="H194" s="14"/>
       <c r="I194" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J194" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K194" s="16"/>
@@ -5166,7 +5310,7 @@
       <c r="M194" s="16"/>
       <c r="N194" s="17"/>
     </row>
-    <row r="195" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A195" s="13"/>
       <c r="B195" s="14"/>
       <c r="C195" s="14"/>
@@ -5176,11 +5320,11 @@
       <c r="G195" s="14"/>
       <c r="H195" s="14"/>
       <c r="I195" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J195" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K195" s="16"/>
@@ -5188,7 +5332,7 @@
       <c r="M195" s="16"/>
       <c r="N195" s="17"/>
     </row>
-    <row r="196" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A196" s="13"/>
       <c r="B196" s="14"/>
       <c r="C196" s="14"/>
@@ -5198,11 +5342,11 @@
       <c r="G196" s="14"/>
       <c r="H196" s="14"/>
       <c r="I196" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J196" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K196" s="16"/>
@@ -5210,7 +5354,7 @@
       <c r="M196" s="16"/>
       <c r="N196" s="17"/>
     </row>
-    <row r="197" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A197" s="13"/>
       <c r="B197" s="14"/>
       <c r="C197" s="14"/>
@@ -5220,11 +5364,11 @@
       <c r="G197" s="14"/>
       <c r="H197" s="14"/>
       <c r="I197" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J197" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K197" s="16"/>
@@ -5232,7 +5376,7 @@
       <c r="M197" s="16"/>
       <c r="N197" s="17"/>
     </row>
-    <row r="198" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A198" s="13"/>
       <c r="B198" s="14"/>
       <c r="C198" s="14"/>
@@ -5242,11 +5386,11 @@
       <c r="G198" s="14"/>
       <c r="H198" s="14"/>
       <c r="I198" s="15" t="str">
-        <f t="shared" ref="I198:I261" si="6">IF(SUM(B198:F198,H198)=0,"",SUM(B198:F198,H198))</f>
+        <f t="shared" ref="I198:I261" si="8">IF(SUM(B198:F198,H198)=0,"",SUM(B198:F198,H198))</f>
         <v/>
       </c>
       <c r="J198" s="15" t="str">
-        <f t="shared" ref="J198:J261" si="7">IF(I198="","",1440-I198)</f>
+        <f t="shared" ref="J198:J261" si="9">IF(I198="","",1440-I198)</f>
         <v/>
       </c>
       <c r="K198" s="16"/>
@@ -5254,7 +5398,7 @@
       <c r="M198" s="16"/>
       <c r="N198" s="17"/>
     </row>
-    <row r="199" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A199" s="13"/>
       <c r="B199" s="14"/>
       <c r="C199" s="14"/>
@@ -5264,11 +5408,11 @@
       <c r="G199" s="14"/>
       <c r="H199" s="14"/>
       <c r="I199" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J199" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K199" s="16"/>
@@ -5276,7 +5420,7 @@
       <c r="M199" s="16"/>
       <c r="N199" s="17"/>
     </row>
-    <row r="200" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A200" s="13"/>
       <c r="B200" s="14"/>
       <c r="C200" s="14"/>
@@ -5286,11 +5430,11 @@
       <c r="G200" s="14"/>
       <c r="H200" s="14"/>
       <c r="I200" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J200" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K200" s="16"/>
@@ -5298,7 +5442,7 @@
       <c r="M200" s="16"/>
       <c r="N200" s="17"/>
     </row>
-    <row r="201" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A201" s="13"/>
       <c r="B201" s="14"/>
       <c r="C201" s="14"/>
@@ -5308,11 +5452,11 @@
       <c r="G201" s="14"/>
       <c r="H201" s="14"/>
       <c r="I201" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J201" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K201" s="16"/>
@@ -5320,7 +5464,7 @@
       <c r="M201" s="16"/>
       <c r="N201" s="17"/>
     </row>
-    <row r="202" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A202" s="13"/>
       <c r="B202" s="14"/>
       <c r="C202" s="14"/>
@@ -5330,11 +5474,11 @@
       <c r="G202" s="14"/>
       <c r="H202" s="14"/>
       <c r="I202" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J202" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K202" s="16"/>
@@ -5342,7 +5486,7 @@
       <c r="M202" s="16"/>
       <c r="N202" s="17"/>
     </row>
-    <row r="203" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A203" s="13"/>
       <c r="B203" s="14"/>
       <c r="C203" s="14"/>
@@ -5352,11 +5496,11 @@
       <c r="G203" s="14"/>
       <c r="H203" s="14"/>
       <c r="I203" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J203" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K203" s="16"/>
@@ -5364,7 +5508,7 @@
       <c r="M203" s="16"/>
       <c r="N203" s="17"/>
     </row>
-    <row r="204" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A204" s="13"/>
       <c r="B204" s="14"/>
       <c r="C204" s="14"/>
@@ -5374,11 +5518,11 @@
       <c r="G204" s="14"/>
       <c r="H204" s="14"/>
       <c r="I204" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J204" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K204" s="16"/>
@@ -5386,7 +5530,7 @@
       <c r="M204" s="16"/>
       <c r="N204" s="17"/>
     </row>
-    <row r="205" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A205" s="13"/>
       <c r="B205" s="14"/>
       <c r="C205" s="14"/>
@@ -5396,11 +5540,11 @@
       <c r="G205" s="14"/>
       <c r="H205" s="14"/>
       <c r="I205" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J205" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K205" s="16"/>
@@ -5408,7 +5552,7 @@
       <c r="M205" s="16"/>
       <c r="N205" s="17"/>
     </row>
-    <row r="206" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A206" s="13"/>
       <c r="B206" s="14"/>
       <c r="C206" s="14"/>
@@ -5418,11 +5562,11 @@
       <c r="G206" s="14"/>
       <c r="H206" s="14"/>
       <c r="I206" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J206" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K206" s="16"/>
@@ -5430,7 +5574,7 @@
       <c r="M206" s="16"/>
       <c r="N206" s="17"/>
     </row>
-    <row r="207" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A207" s="13"/>
       <c r="B207" s="14"/>
       <c r="C207" s="14"/>
@@ -5440,11 +5584,11 @@
       <c r="G207" s="14"/>
       <c r="H207" s="14"/>
       <c r="I207" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J207" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K207" s="16"/>
@@ -5452,7 +5596,7 @@
       <c r="M207" s="16"/>
       <c r="N207" s="17"/>
     </row>
-    <row r="208" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A208" s="13"/>
       <c r="B208" s="14"/>
       <c r="C208" s="14"/>
@@ -5462,11 +5606,11 @@
       <c r="G208" s="14"/>
       <c r="H208" s="14"/>
       <c r="I208" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J208" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K208" s="16"/>
@@ -5474,7 +5618,7 @@
       <c r="M208" s="16"/>
       <c r="N208" s="17"/>
     </row>
-    <row r="209" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A209" s="13"/>
       <c r="B209" s="14"/>
       <c r="C209" s="14"/>
@@ -5484,11 +5628,11 @@
       <c r="G209" s="14"/>
       <c r="H209" s="14"/>
       <c r="I209" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J209" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K209" s="16"/>
@@ -5496,7 +5640,7 @@
       <c r="M209" s="16"/>
       <c r="N209" s="17"/>
     </row>
-    <row r="210" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A210" s="13"/>
       <c r="B210" s="14"/>
       <c r="C210" s="14"/>
@@ -5506,11 +5650,11 @@
       <c r="G210" s="14"/>
       <c r="H210" s="14"/>
       <c r="I210" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J210" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K210" s="16"/>
@@ -5518,7 +5662,7 @@
       <c r="M210" s="16"/>
       <c r="N210" s="17"/>
     </row>
-    <row r="211" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A211" s="13"/>
       <c r="B211" s="14"/>
       <c r="C211" s="14"/>
@@ -5528,11 +5672,11 @@
       <c r="G211" s="14"/>
       <c r="H211" s="14"/>
       <c r="I211" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J211" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K211" s="16"/>
@@ -5540,7 +5684,7 @@
       <c r="M211" s="16"/>
       <c r="N211" s="17"/>
     </row>
-    <row r="212" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A212" s="13"/>
       <c r="B212" s="14"/>
       <c r="C212" s="14"/>
@@ -5550,11 +5694,11 @@
       <c r="G212" s="14"/>
       <c r="H212" s="14"/>
       <c r="I212" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J212" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K212" s="16"/>
@@ -5562,7 +5706,7 @@
       <c r="M212" s="16"/>
       <c r="N212" s="17"/>
     </row>
-    <row r="213" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A213" s="13"/>
       <c r="B213" s="14"/>
       <c r="C213" s="14"/>
@@ -5572,11 +5716,11 @@
       <c r="G213" s="14"/>
       <c r="H213" s="14"/>
       <c r="I213" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J213" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K213" s="16"/>
@@ -5584,7 +5728,7 @@
       <c r="M213" s="16"/>
       <c r="N213" s="17"/>
     </row>
-    <row r="214" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A214" s="13"/>
       <c r="B214" s="14"/>
       <c r="C214" s="14"/>
@@ -5594,11 +5738,11 @@
       <c r="G214" s="14"/>
       <c r="H214" s="14"/>
       <c r="I214" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J214" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K214" s="16"/>
@@ -5606,7 +5750,7 @@
       <c r="M214" s="16"/>
       <c r="N214" s="17"/>
     </row>
-    <row r="215" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A215" s="13"/>
       <c r="B215" s="14"/>
       <c r="C215" s="14"/>
@@ -5616,11 +5760,11 @@
       <c r="G215" s="14"/>
       <c r="H215" s="14"/>
       <c r="I215" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J215" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K215" s="16"/>
@@ -5628,7 +5772,7 @@
       <c r="M215" s="16"/>
       <c r="N215" s="17"/>
     </row>
-    <row r="216" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A216" s="13"/>
       <c r="B216" s="14"/>
       <c r="C216" s="14"/>
@@ -5638,11 +5782,11 @@
       <c r="G216" s="14"/>
       <c r="H216" s="14"/>
       <c r="I216" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J216" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K216" s="16"/>
@@ -5650,7 +5794,7 @@
       <c r="M216" s="16"/>
       <c r="N216" s="17"/>
     </row>
-    <row r="217" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A217" s="13"/>
       <c r="B217" s="14"/>
       <c r="C217" s="14"/>
@@ -5660,11 +5804,11 @@
       <c r="G217" s="14"/>
       <c r="H217" s="14"/>
       <c r="I217" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J217" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K217" s="16"/>
@@ -5672,7 +5816,7 @@
       <c r="M217" s="16"/>
       <c r="N217" s="17"/>
     </row>
-    <row r="218" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A218" s="13"/>
       <c r="B218" s="14"/>
       <c r="C218" s="14"/>
@@ -5682,11 +5826,11 @@
       <c r="G218" s="14"/>
       <c r="H218" s="14"/>
       <c r="I218" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J218" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K218" s="16"/>
@@ -5694,7 +5838,7 @@
       <c r="M218" s="16"/>
       <c r="N218" s="17"/>
     </row>
-    <row r="219" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A219" s="13"/>
       <c r="B219" s="14"/>
       <c r="C219" s="14"/>
@@ -5704,11 +5848,11 @@
       <c r="G219" s="14"/>
       <c r="H219" s="14"/>
       <c r="I219" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J219" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K219" s="16"/>
@@ -5716,7 +5860,7 @@
       <c r="M219" s="16"/>
       <c r="N219" s="17"/>
     </row>
-    <row r="220" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A220" s="13"/>
       <c r="B220" s="14"/>
       <c r="C220" s="14"/>
@@ -5726,11 +5870,11 @@
       <c r="G220" s="14"/>
       <c r="H220" s="14"/>
       <c r="I220" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J220" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K220" s="16"/>
@@ -5738,7 +5882,7 @@
       <c r="M220" s="16"/>
       <c r="N220" s="17"/>
     </row>
-    <row r="221" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A221" s="13"/>
       <c r="B221" s="14"/>
       <c r="C221" s="14"/>
@@ -5748,11 +5892,11 @@
       <c r="G221" s="14"/>
       <c r="H221" s="14"/>
       <c r="I221" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J221" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K221" s="16"/>
@@ -5760,7 +5904,7 @@
       <c r="M221" s="16"/>
       <c r="N221" s="17"/>
     </row>
-    <row r="222" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A222" s="13"/>
       <c r="B222" s="14"/>
       <c r="C222" s="14"/>
@@ -5770,11 +5914,11 @@
       <c r="G222" s="14"/>
       <c r="H222" s="14"/>
       <c r="I222" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J222" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K222" s="16"/>
@@ -5782,7 +5926,7 @@
       <c r="M222" s="16"/>
       <c r="N222" s="17"/>
     </row>
-    <row r="223" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A223" s="13"/>
       <c r="B223" s="14"/>
       <c r="C223" s="14"/>
@@ -5792,11 +5936,11 @@
       <c r="G223" s="14"/>
       <c r="H223" s="14"/>
       <c r="I223" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J223" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K223" s="16"/>
@@ -5804,7 +5948,7 @@
       <c r="M223" s="16"/>
       <c r="N223" s="17"/>
     </row>
-    <row r="224" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A224" s="13"/>
       <c r="B224" s="14"/>
       <c r="C224" s="14"/>
@@ -5814,11 +5958,11 @@
       <c r="G224" s="14"/>
       <c r="H224" s="14"/>
       <c r="I224" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J224" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K224" s="16"/>
@@ -5826,7 +5970,7 @@
       <c r="M224" s="16"/>
       <c r="N224" s="17"/>
     </row>
-    <row r="225" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A225" s="13"/>
       <c r="B225" s="14"/>
       <c r="C225" s="14"/>
@@ -5836,11 +5980,11 @@
       <c r="G225" s="14"/>
       <c r="H225" s="14"/>
       <c r="I225" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J225" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K225" s="16"/>
@@ -5848,7 +5992,7 @@
       <c r="M225" s="16"/>
       <c r="N225" s="17"/>
     </row>
-    <row r="226" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A226" s="13"/>
       <c r="B226" s="14"/>
       <c r="C226" s="14"/>
@@ -5858,11 +6002,11 @@
       <c r="G226" s="14"/>
       <c r="H226" s="14"/>
       <c r="I226" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J226" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K226" s="16"/>
@@ -5870,7 +6014,7 @@
       <c r="M226" s="16"/>
       <c r="N226" s="17"/>
     </row>
-    <row r="227" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A227" s="13"/>
       <c r="B227" s="14"/>
       <c r="C227" s="14"/>
@@ -5880,11 +6024,11 @@
       <c r="G227" s="14"/>
       <c r="H227" s="14"/>
       <c r="I227" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J227" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K227" s="16"/>
@@ -5892,7 +6036,7 @@
       <c r="M227" s="16"/>
       <c r="N227" s="17"/>
     </row>
-    <row r="228" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A228" s="13"/>
       <c r="B228" s="14"/>
       <c r="C228" s="14"/>
@@ -5902,11 +6046,11 @@
       <c r="G228" s="14"/>
       <c r="H228" s="14"/>
       <c r="I228" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J228" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K228" s="16"/>
@@ -5914,7 +6058,7 @@
       <c r="M228" s="16"/>
       <c r="N228" s="17"/>
     </row>
-    <row r="229" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A229" s="13"/>
       <c r="B229" s="14"/>
       <c r="C229" s="14"/>
@@ -5924,11 +6068,11 @@
       <c r="G229" s="14"/>
       <c r="H229" s="14"/>
       <c r="I229" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J229" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K229" s="16"/>
@@ -5936,7 +6080,7 @@
       <c r="M229" s="16"/>
       <c r="N229" s="17"/>
     </row>
-    <row r="230" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A230" s="13"/>
       <c r="B230" s="14"/>
       <c r="C230" s="14"/>
@@ -5946,11 +6090,11 @@
       <c r="G230" s="14"/>
       <c r="H230" s="14"/>
       <c r="I230" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J230" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K230" s="16"/>
@@ -5958,7 +6102,7 @@
       <c r="M230" s="16"/>
       <c r="N230" s="17"/>
     </row>
-    <row r="231" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A231" s="13"/>
       <c r="B231" s="14"/>
       <c r="C231" s="14"/>
@@ -5968,11 +6112,11 @@
       <c r="G231" s="14"/>
       <c r="H231" s="14"/>
       <c r="I231" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J231" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K231" s="16"/>
@@ -5980,7 +6124,7 @@
       <c r="M231" s="16"/>
       <c r="N231" s="17"/>
     </row>
-    <row r="232" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A232" s="13"/>
       <c r="B232" s="14"/>
       <c r="C232" s="14"/>
@@ -5990,11 +6134,11 @@
       <c r="G232" s="14"/>
       <c r="H232" s="14"/>
       <c r="I232" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J232" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K232" s="16"/>
@@ -6002,7 +6146,7 @@
       <c r="M232" s="16"/>
       <c r="N232" s="17"/>
     </row>
-    <row r="233" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A233" s="13"/>
       <c r="B233" s="14"/>
       <c r="C233" s="14"/>
@@ -6012,11 +6156,11 @@
       <c r="G233" s="14"/>
       <c r="H233" s="14"/>
       <c r="I233" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J233" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K233" s="16"/>
@@ -6024,7 +6168,7 @@
       <c r="M233" s="16"/>
       <c r="N233" s="17"/>
     </row>
-    <row r="234" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A234" s="13"/>
       <c r="B234" s="14"/>
       <c r="C234" s="14"/>
@@ -6034,11 +6178,11 @@
       <c r="G234" s="14"/>
       <c r="H234" s="14"/>
       <c r="I234" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J234" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K234" s="16"/>
@@ -6046,7 +6190,7 @@
       <c r="M234" s="16"/>
       <c r="N234" s="17"/>
     </row>
-    <row r="235" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A235" s="13"/>
       <c r="B235" s="14"/>
       <c r="C235" s="14"/>
@@ -6056,11 +6200,11 @@
       <c r="G235" s="14"/>
       <c r="H235" s="14"/>
       <c r="I235" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J235" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K235" s="16"/>
@@ -6068,7 +6212,7 @@
       <c r="M235" s="16"/>
       <c r="N235" s="17"/>
     </row>
-    <row r="236" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A236" s="13"/>
       <c r="B236" s="14"/>
       <c r="C236" s="14"/>
@@ -6078,11 +6222,11 @@
       <c r="G236" s="14"/>
       <c r="H236" s="14"/>
       <c r="I236" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J236" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K236" s="16"/>
@@ -6090,7 +6234,7 @@
       <c r="M236" s="16"/>
       <c r="N236" s="17"/>
     </row>
-    <row r="237" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A237" s="13"/>
       <c r="B237" s="14"/>
       <c r="C237" s="14"/>
@@ -6100,11 +6244,11 @@
       <c r="G237" s="14"/>
       <c r="H237" s="14"/>
       <c r="I237" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J237" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K237" s="16"/>
@@ -6112,7 +6256,7 @@
       <c r="M237" s="16"/>
       <c r="N237" s="17"/>
     </row>
-    <row r="238" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A238" s="13"/>
       <c r="B238" s="14"/>
       <c r="C238" s="14"/>
@@ -6122,11 +6266,11 @@
       <c r="G238" s="14"/>
       <c r="H238" s="14"/>
       <c r="I238" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J238" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K238" s="16"/>
@@ -6134,7 +6278,7 @@
       <c r="M238" s="16"/>
       <c r="N238" s="17"/>
     </row>
-    <row r="239" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A239" s="13"/>
       <c r="B239" s="14"/>
       <c r="C239" s="14"/>
@@ -6144,11 +6288,11 @@
       <c r="G239" s="14"/>
       <c r="H239" s="14"/>
       <c r="I239" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J239" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K239" s="16"/>
@@ -6156,7 +6300,7 @@
       <c r="M239" s="16"/>
       <c r="N239" s="17"/>
     </row>
-    <row r="240" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A240" s="13"/>
       <c r="B240" s="14"/>
       <c r="C240" s="14"/>
@@ -6166,11 +6310,11 @@
       <c r="G240" s="14"/>
       <c r="H240" s="14"/>
       <c r="I240" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J240" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K240" s="16"/>
@@ -6178,7 +6322,7 @@
       <c r="M240" s="16"/>
       <c r="N240" s="17"/>
     </row>
-    <row r="241" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A241" s="13"/>
       <c r="B241" s="14"/>
       <c r="C241" s="14"/>
@@ -6188,11 +6332,11 @@
       <c r="G241" s="14"/>
       <c r="H241" s="14"/>
       <c r="I241" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J241" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K241" s="16"/>
@@ -6200,7 +6344,7 @@
       <c r="M241" s="16"/>
       <c r="N241" s="17"/>
     </row>
-    <row r="242" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A242" s="13"/>
       <c r="B242" s="14"/>
       <c r="C242" s="14"/>
@@ -6210,11 +6354,11 @@
       <c r="G242" s="14"/>
       <c r="H242" s="14"/>
       <c r="I242" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J242" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K242" s="16"/>
@@ -6222,7 +6366,7 @@
       <c r="M242" s="16"/>
       <c r="N242" s="17"/>
     </row>
-    <row r="243" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A243" s="13"/>
       <c r="B243" s="14"/>
       <c r="C243" s="14"/>
@@ -6232,11 +6376,11 @@
       <c r="G243" s="14"/>
       <c r="H243" s="14"/>
       <c r="I243" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J243" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K243" s="16"/>
@@ -6244,7 +6388,7 @@
       <c r="M243" s="16"/>
       <c r="N243" s="17"/>
     </row>
-    <row r="244" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A244" s="13"/>
       <c r="B244" s="14"/>
       <c r="C244" s="14"/>
@@ -6254,11 +6398,11 @@
       <c r="G244" s="14"/>
       <c r="H244" s="14"/>
       <c r="I244" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J244" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K244" s="16"/>
@@ -6266,7 +6410,7 @@
       <c r="M244" s="16"/>
       <c r="N244" s="17"/>
     </row>
-    <row r="245" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A245" s="13"/>
       <c r="B245" s="14"/>
       <c r="C245" s="14"/>
@@ -6276,11 +6420,11 @@
       <c r="G245" s="14"/>
       <c r="H245" s="14"/>
       <c r="I245" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J245" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K245" s="16"/>
@@ -6288,7 +6432,7 @@
       <c r="M245" s="16"/>
       <c r="N245" s="17"/>
     </row>
-    <row r="246" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A246" s="13"/>
       <c r="B246" s="14"/>
       <c r="C246" s="14"/>
@@ -6298,11 +6442,11 @@
       <c r="G246" s="14"/>
       <c r="H246" s="14"/>
       <c r="I246" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J246" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K246" s="16"/>
@@ -6310,7 +6454,7 @@
       <c r="M246" s="16"/>
       <c r="N246" s="17"/>
     </row>
-    <row r="247" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A247" s="13"/>
       <c r="B247" s="14"/>
       <c r="C247" s="14"/>
@@ -6320,11 +6464,11 @@
       <c r="G247" s="14"/>
       <c r="H247" s="14"/>
       <c r="I247" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J247" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K247" s="16"/>
@@ -6332,7 +6476,7 @@
       <c r="M247" s="16"/>
       <c r="N247" s="17"/>
     </row>
-    <row r="248" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A248" s="13"/>
       <c r="B248" s="14"/>
       <c r="C248" s="14"/>
@@ -6342,11 +6486,11 @@
       <c r="G248" s="14"/>
       <c r="H248" s="14"/>
       <c r="I248" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J248" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K248" s="16"/>
@@ -6354,7 +6498,7 @@
       <c r="M248" s="16"/>
       <c r="N248" s="17"/>
     </row>
-    <row r="249" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A249" s="13"/>
       <c r="B249" s="14"/>
       <c r="C249" s="14"/>
@@ -6364,11 +6508,11 @@
       <c r="G249" s="14"/>
       <c r="H249" s="14"/>
       <c r="I249" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J249" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K249" s="16"/>
@@ -6376,7 +6520,7 @@
       <c r="M249" s="16"/>
       <c r="N249" s="17"/>
     </row>
-    <row r="250" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A250" s="13"/>
       <c r="B250" s="14"/>
       <c r="C250" s="14"/>
@@ -6386,11 +6530,11 @@
       <c r="G250" s="14"/>
       <c r="H250" s="14"/>
       <c r="I250" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J250" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K250" s="16"/>
@@ -6398,7 +6542,7 @@
       <c r="M250" s="16"/>
       <c r="N250" s="17"/>
     </row>
-    <row r="251" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A251" s="13"/>
       <c r="B251" s="14"/>
       <c r="C251" s="14"/>
@@ -6408,11 +6552,11 @@
       <c r="G251" s="14"/>
       <c r="H251" s="14"/>
       <c r="I251" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J251" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K251" s="16"/>
@@ -6420,7 +6564,7 @@
       <c r="M251" s="16"/>
       <c r="N251" s="17"/>
     </row>
-    <row r="252" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A252" s="13"/>
       <c r="B252" s="14"/>
       <c r="C252" s="14"/>
@@ -6430,11 +6574,11 @@
       <c r="G252" s="14"/>
       <c r="H252" s="14"/>
       <c r="I252" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J252" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K252" s="16"/>
@@ -6442,7 +6586,7 @@
       <c r="M252" s="16"/>
       <c r="N252" s="17"/>
     </row>
-    <row r="253" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A253" s="13"/>
       <c r="B253" s="14"/>
       <c r="C253" s="14"/>
@@ -6452,11 +6596,11 @@
       <c r="G253" s="14"/>
       <c r="H253" s="14"/>
       <c r="I253" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J253" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K253" s="16"/>
@@ -6464,7 +6608,7 @@
       <c r="M253" s="16"/>
       <c r="N253" s="17"/>
     </row>
-    <row r="254" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A254" s="13"/>
       <c r="B254" s="14"/>
       <c r="C254" s="14"/>
@@ -6474,11 +6618,11 @@
       <c r="G254" s="14"/>
       <c r="H254" s="14"/>
       <c r="I254" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J254" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K254" s="16"/>
@@ -6486,7 +6630,7 @@
       <c r="M254" s="16"/>
       <c r="N254" s="17"/>
     </row>
-    <row r="255" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A255" s="13"/>
       <c r="B255" s="14"/>
       <c r="C255" s="14"/>
@@ -6496,11 +6640,11 @@
       <c r="G255" s="14"/>
       <c r="H255" s="14"/>
       <c r="I255" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J255" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K255" s="16"/>
@@ -6508,7 +6652,7 @@
       <c r="M255" s="16"/>
       <c r="N255" s="17"/>
     </row>
-    <row r="256" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A256" s="13"/>
       <c r="B256" s="14"/>
       <c r="C256" s="14"/>
@@ -6518,11 +6662,11 @@
       <c r="G256" s="14"/>
       <c r="H256" s="14"/>
       <c r="I256" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J256" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K256" s="16"/>
@@ -6530,7 +6674,7 @@
       <c r="M256" s="16"/>
       <c r="N256" s="17"/>
     </row>
-    <row r="257" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A257" s="13"/>
       <c r="B257" s="14"/>
       <c r="C257" s="14"/>
@@ -6540,11 +6684,11 @@
       <c r="G257" s="14"/>
       <c r="H257" s="14"/>
       <c r="I257" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J257" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K257" s="16"/>
@@ -6552,7 +6696,7 @@
       <c r="M257" s="16"/>
       <c r="N257" s="17"/>
     </row>
-    <row r="258" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A258" s="13"/>
       <c r="B258" s="14"/>
       <c r="C258" s="14"/>
@@ -6562,11 +6706,11 @@
       <c r="G258" s="14"/>
       <c r="H258" s="14"/>
       <c r="I258" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J258" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K258" s="16"/>
@@ -6574,7 +6718,7 @@
       <c r="M258" s="16"/>
       <c r="N258" s="17"/>
     </row>
-    <row r="259" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A259" s="13"/>
       <c r="B259" s="14"/>
       <c r="C259" s="14"/>
@@ -6584,11 +6728,11 @@
       <c r="G259" s="14"/>
       <c r="H259" s="14"/>
       <c r="I259" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J259" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K259" s="16"/>
@@ -6596,7 +6740,7 @@
       <c r="M259" s="16"/>
       <c r="N259" s="17"/>
     </row>
-    <row r="260" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A260" s="13"/>
       <c r="B260" s="14"/>
       <c r="C260" s="14"/>
@@ -6606,11 +6750,11 @@
       <c r="G260" s="14"/>
       <c r="H260" s="14"/>
       <c r="I260" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J260" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K260" s="16"/>
@@ -6618,7 +6762,7 @@
       <c r="M260" s="16"/>
       <c r="N260" s="17"/>
     </row>
-    <row r="261" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A261" s="13"/>
       <c r="B261" s="14"/>
       <c r="C261" s="14"/>
@@ -6628,11 +6772,11 @@
       <c r="G261" s="14"/>
       <c r="H261" s="14"/>
       <c r="I261" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J261" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K261" s="16"/>
@@ -6640,7 +6784,7 @@
       <c r="M261" s="16"/>
       <c r="N261" s="17"/>
     </row>
-    <row r="262" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A262" s="13"/>
       <c r="B262" s="14"/>
       <c r="C262" s="14"/>
@@ -6650,11 +6794,11 @@
       <c r="G262" s="14"/>
       <c r="H262" s="14"/>
       <c r="I262" s="15" t="str">
-        <f t="shared" ref="I262:I325" si="8">IF(SUM(B262:F262,H262)=0,"",SUM(B262:F262,H262))</f>
+        <f t="shared" ref="I262:I325" si="10">IF(SUM(B262:F262,H262)=0,"",SUM(B262:F262,H262))</f>
         <v/>
       </c>
       <c r="J262" s="15" t="str">
-        <f t="shared" ref="J262:J325" si="9">IF(I262="","",1440-I262)</f>
+        <f t="shared" ref="J262:J325" si="11">IF(I262="","",1440-I262)</f>
         <v/>
       </c>
       <c r="K262" s="16"/>
@@ -6662,7 +6806,7 @@
       <c r="M262" s="16"/>
       <c r="N262" s="17"/>
     </row>
-    <row r="263" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A263" s="13"/>
       <c r="B263" s="14"/>
       <c r="C263" s="14"/>
@@ -6672,11 +6816,11 @@
       <c r="G263" s="14"/>
       <c r="H263" s="14"/>
       <c r="I263" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J263" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K263" s="16"/>
@@ -6684,7 +6828,7 @@
       <c r="M263" s="16"/>
       <c r="N263" s="17"/>
     </row>
-    <row r="264" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A264" s="13"/>
       <c r="B264" s="14"/>
       <c r="C264" s="14"/>
@@ -6694,11 +6838,11 @@
       <c r="G264" s="14"/>
       <c r="H264" s="14"/>
       <c r="I264" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J264" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K264" s="16"/>
@@ -6706,7 +6850,7 @@
       <c r="M264" s="16"/>
       <c r="N264" s="17"/>
     </row>
-    <row r="265" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A265" s="13"/>
       <c r="B265" s="14"/>
       <c r="C265" s="14"/>
@@ -6716,11 +6860,11 @@
       <c r="G265" s="14"/>
       <c r="H265" s="14"/>
       <c r="I265" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J265" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K265" s="16"/>
@@ -6728,7 +6872,7 @@
       <c r="M265" s="16"/>
       <c r="N265" s="17"/>
     </row>
-    <row r="266" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A266" s="13"/>
       <c r="B266" s="14"/>
       <c r="C266" s="14"/>
@@ -6738,11 +6882,11 @@
       <c r="G266" s="14"/>
       <c r="H266" s="14"/>
       <c r="I266" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J266" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K266" s="16"/>
@@ -6750,7 +6894,7 @@
       <c r="M266" s="16"/>
       <c r="N266" s="17"/>
     </row>
-    <row r="267" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A267" s="13"/>
       <c r="B267" s="14"/>
       <c r="C267" s="14"/>
@@ -6760,11 +6904,11 @@
       <c r="G267" s="14"/>
       <c r="H267" s="14"/>
       <c r="I267" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J267" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K267" s="16"/>
@@ -6772,7 +6916,7 @@
       <c r="M267" s="16"/>
       <c r="N267" s="17"/>
     </row>
-    <row r="268" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A268" s="13"/>
       <c r="B268" s="14"/>
       <c r="C268" s="14"/>
@@ -6782,11 +6926,11 @@
       <c r="G268" s="14"/>
       <c r="H268" s="14"/>
       <c r="I268" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J268" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K268" s="16"/>
@@ -6794,7 +6938,7 @@
       <c r="M268" s="16"/>
       <c r="N268" s="17"/>
     </row>
-    <row r="269" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A269" s="13"/>
       <c r="B269" s="14"/>
       <c r="C269" s="14"/>
@@ -6804,11 +6948,11 @@
       <c r="G269" s="14"/>
       <c r="H269" s="14"/>
       <c r="I269" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J269" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K269" s="16"/>
@@ -6816,7 +6960,7 @@
       <c r="M269" s="16"/>
       <c r="N269" s="17"/>
     </row>
-    <row r="270" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A270" s="13"/>
       <c r="B270" s="14"/>
       <c r="C270" s="14"/>
@@ -6826,11 +6970,11 @@
       <c r="G270" s="14"/>
       <c r="H270" s="14"/>
       <c r="I270" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J270" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K270" s="16"/>
@@ -6838,7 +6982,7 @@
       <c r="M270" s="16"/>
       <c r="N270" s="17"/>
     </row>
-    <row r="271" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A271" s="13"/>
       <c r="B271" s="14"/>
       <c r="C271" s="14"/>
@@ -6848,11 +6992,11 @@
       <c r="G271" s="14"/>
       <c r="H271" s="14"/>
       <c r="I271" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J271" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K271" s="16"/>
@@ -6860,7 +7004,7 @@
       <c r="M271" s="16"/>
       <c r="N271" s="17"/>
     </row>
-    <row r="272" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A272" s="13"/>
       <c r="B272" s="14"/>
       <c r="C272" s="14"/>
@@ -6870,11 +7014,11 @@
       <c r="G272" s="14"/>
       <c r="H272" s="14"/>
       <c r="I272" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J272" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K272" s="16"/>
@@ -6882,7 +7026,7 @@
       <c r="M272" s="16"/>
       <c r="N272" s="17"/>
     </row>
-    <row r="273" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A273" s="13"/>
       <c r="B273" s="14"/>
       <c r="C273" s="14"/>
@@ -6892,11 +7036,11 @@
       <c r="G273" s="14"/>
       <c r="H273" s="14"/>
       <c r="I273" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J273" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K273" s="16"/>
@@ -6904,7 +7048,7 @@
       <c r="M273" s="16"/>
       <c r="N273" s="17"/>
     </row>
-    <row r="274" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A274" s="13"/>
       <c r="B274" s="14"/>
       <c r="C274" s="14"/>
@@ -6914,11 +7058,11 @@
       <c r="G274" s="14"/>
       <c r="H274" s="14"/>
       <c r="I274" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J274" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K274" s="16"/>
@@ -6926,7 +7070,7 @@
       <c r="M274" s="16"/>
       <c r="N274" s="17"/>
     </row>
-    <row r="275" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A275" s="13"/>
       <c r="B275" s="14"/>
       <c r="C275" s="14"/>
@@ -6936,11 +7080,11 @@
       <c r="G275" s="14"/>
       <c r="H275" s="14"/>
       <c r="I275" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J275" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K275" s="16"/>
@@ -6948,7 +7092,7 @@
       <c r="M275" s="16"/>
       <c r="N275" s="17"/>
     </row>
-    <row r="276" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A276" s="13"/>
       <c r="B276" s="14"/>
       <c r="C276" s="14"/>
@@ -6958,11 +7102,11 @@
       <c r="G276" s="14"/>
       <c r="H276" s="14"/>
       <c r="I276" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J276" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K276" s="16"/>
@@ -6970,7 +7114,7 @@
       <c r="M276" s="16"/>
       <c r="N276" s="17"/>
     </row>
-    <row r="277" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A277" s="13"/>
       <c r="B277" s="14"/>
       <c r="C277" s="14"/>
@@ -6980,11 +7124,11 @@
       <c r="G277" s="14"/>
       <c r="H277" s="14"/>
       <c r="I277" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J277" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K277" s="16"/>
@@ -6992,7 +7136,7 @@
       <c r="M277" s="16"/>
       <c r="N277" s="17"/>
     </row>
-    <row r="278" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A278" s="13"/>
       <c r="B278" s="14"/>
       <c r="C278" s="14"/>
@@ -7002,11 +7146,11 @@
       <c r="G278" s="14"/>
       <c r="H278" s="14"/>
       <c r="I278" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J278" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K278" s="16"/>
@@ -7014,7 +7158,7 @@
       <c r="M278" s="16"/>
       <c r="N278" s="17"/>
     </row>
-    <row r="279" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A279" s="13"/>
       <c r="B279" s="14"/>
       <c r="C279" s="14"/>
@@ -7024,11 +7168,11 @@
       <c r="G279" s="14"/>
       <c r="H279" s="14"/>
       <c r="I279" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J279" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K279" s="16"/>
@@ -7036,7 +7180,7 @@
       <c r="M279" s="16"/>
       <c r="N279" s="17"/>
     </row>
-    <row r="280" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A280" s="13"/>
       <c r="B280" s="14"/>
       <c r="C280" s="14"/>
@@ -7046,11 +7190,11 @@
       <c r="G280" s="14"/>
       <c r="H280" s="14"/>
       <c r="I280" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J280" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K280" s="16"/>
@@ -7058,7 +7202,7 @@
       <c r="M280" s="16"/>
       <c r="N280" s="17"/>
     </row>
-    <row r="281" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A281" s="13"/>
       <c r="B281" s="14"/>
       <c r="C281" s="14"/>
@@ -7068,11 +7212,11 @@
       <c r="G281" s="14"/>
       <c r="H281" s="14"/>
       <c r="I281" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J281" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K281" s="16"/>
@@ -7080,7 +7224,7 @@
       <c r="M281" s="16"/>
       <c r="N281" s="17"/>
     </row>
-    <row r="282" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A282" s="13"/>
       <c r="B282" s="14"/>
       <c r="C282" s="14"/>
@@ -7090,11 +7234,11 @@
       <c r="G282" s="14"/>
       <c r="H282" s="14"/>
       <c r="I282" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J282" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K282" s="16"/>
@@ -7102,7 +7246,7 @@
       <c r="M282" s="16"/>
       <c r="N282" s="17"/>
     </row>
-    <row r="283" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A283" s="13"/>
       <c r="B283" s="14"/>
       <c r="C283" s="14"/>
@@ -7112,11 +7256,11 @@
       <c r="G283" s="14"/>
       <c r="H283" s="14"/>
       <c r="I283" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J283" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K283" s="16"/>
@@ -7124,7 +7268,7 @@
       <c r="M283" s="16"/>
       <c r="N283" s="17"/>
     </row>
-    <row r="284" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A284" s="13"/>
       <c r="B284" s="14"/>
       <c r="C284" s="14"/>
@@ -7134,11 +7278,11 @@
       <c r="G284" s="14"/>
       <c r="H284" s="14"/>
       <c r="I284" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J284" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K284" s="16"/>
@@ -7146,7 +7290,7 @@
       <c r="M284" s="16"/>
       <c r="N284" s="17"/>
     </row>
-    <row r="285" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A285" s="13"/>
       <c r="B285" s="14"/>
       <c r="C285" s="14"/>
@@ -7156,11 +7300,11 @@
       <c r="G285" s="14"/>
       <c r="H285" s="14"/>
       <c r="I285" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J285" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K285" s="16"/>
@@ -7168,7 +7312,7 @@
       <c r="M285" s="16"/>
       <c r="N285" s="17"/>
     </row>
-    <row r="286" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A286" s="13"/>
       <c r="B286" s="14"/>
       <c r="C286" s="14"/>
@@ -7178,11 +7322,11 @@
       <c r="G286" s="14"/>
       <c r="H286" s="14"/>
       <c r="I286" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J286" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K286" s="16"/>
@@ -7190,7 +7334,7 @@
       <c r="M286" s="16"/>
       <c r="N286" s="17"/>
     </row>
-    <row r="287" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A287" s="13"/>
       <c r="B287" s="14"/>
       <c r="C287" s="14"/>
@@ -7200,11 +7344,11 @@
       <c r="G287" s="14"/>
       <c r="H287" s="14"/>
       <c r="I287" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J287" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K287" s="16"/>
@@ -7212,7 +7356,7 @@
       <c r="M287" s="16"/>
       <c r="N287" s="17"/>
     </row>
-    <row r="288" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A288" s="13"/>
       <c r="B288" s="14"/>
       <c r="C288" s="14"/>
@@ -7222,11 +7366,11 @@
       <c r="G288" s="14"/>
       <c r="H288" s="14"/>
       <c r="I288" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J288" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K288" s="16"/>
@@ -7234,7 +7378,7 @@
       <c r="M288" s="16"/>
       <c r="N288" s="17"/>
     </row>
-    <row r="289" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A289" s="13"/>
       <c r="B289" s="14"/>
       <c r="C289" s="14"/>
@@ -7244,11 +7388,11 @@
       <c r="G289" s="14"/>
       <c r="H289" s="14"/>
       <c r="I289" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J289" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K289" s="16"/>
@@ -7256,7 +7400,7 @@
       <c r="M289" s="16"/>
       <c r="N289" s="17"/>
     </row>
-    <row r="290" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A290" s="13"/>
       <c r="B290" s="14"/>
       <c r="C290" s="14"/>
@@ -7266,11 +7410,11 @@
       <c r="G290" s="14"/>
       <c r="H290" s="14"/>
       <c r="I290" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J290" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K290" s="16"/>
@@ -7278,7 +7422,7 @@
       <c r="M290" s="16"/>
       <c r="N290" s="17"/>
     </row>
-    <row r="291" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A291" s="13"/>
       <c r="B291" s="14"/>
       <c r="C291" s="14"/>
@@ -7288,11 +7432,11 @@
       <c r="G291" s="14"/>
       <c r="H291" s="14"/>
       <c r="I291" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J291" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K291" s="16"/>
@@ -7300,7 +7444,7 @@
       <c r="M291" s="16"/>
       <c r="N291" s="17"/>
     </row>
-    <row r="292" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A292" s="13"/>
       <c r="B292" s="14"/>
       <c r="C292" s="14"/>
@@ -7310,11 +7454,11 @@
       <c r="G292" s="14"/>
       <c r="H292" s="14"/>
       <c r="I292" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J292" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K292" s="16"/>
@@ -7322,7 +7466,7 @@
       <c r="M292" s="16"/>
       <c r="N292" s="17"/>
     </row>
-    <row r="293" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A293" s="13"/>
       <c r="B293" s="14"/>
       <c r="C293" s="14"/>
@@ -7332,11 +7476,11 @@
       <c r="G293" s="14"/>
       <c r="H293" s="14"/>
       <c r="I293" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J293" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K293" s="16"/>
@@ -7344,7 +7488,7 @@
       <c r="M293" s="16"/>
       <c r="N293" s="17"/>
     </row>
-    <row r="294" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A294" s="13"/>
       <c r="B294" s="14"/>
       <c r="C294" s="14"/>
@@ -7354,11 +7498,11 @@
       <c r="G294" s="14"/>
       <c r="H294" s="14"/>
       <c r="I294" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J294" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K294" s="16"/>
@@ -7366,7 +7510,7 @@
       <c r="M294" s="16"/>
       <c r="N294" s="17"/>
     </row>
-    <row r="295" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A295" s="13"/>
       <c r="B295" s="14"/>
       <c r="C295" s="14"/>
@@ -7376,11 +7520,11 @@
       <c r="G295" s="14"/>
       <c r="H295" s="14"/>
       <c r="I295" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J295" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K295" s="16"/>
@@ -7388,7 +7532,7 @@
       <c r="M295" s="16"/>
       <c r="N295" s="17"/>
     </row>
-    <row r="296" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A296" s="13"/>
       <c r="B296" s="14"/>
       <c r="C296" s="14"/>
@@ -7398,11 +7542,11 @@
       <c r="G296" s="14"/>
       <c r="H296" s="14"/>
       <c r="I296" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J296" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K296" s="16"/>
@@ -7410,7 +7554,7 @@
       <c r="M296" s="16"/>
       <c r="N296" s="17"/>
     </row>
-    <row r="297" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A297" s="13"/>
       <c r="B297" s="14"/>
       <c r="C297" s="14"/>
@@ -7420,11 +7564,11 @@
       <c r="G297" s="14"/>
       <c r="H297" s="14"/>
       <c r="I297" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J297" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K297" s="16"/>
@@ -7432,7 +7576,7 @@
       <c r="M297" s="16"/>
       <c r="N297" s="17"/>
     </row>
-    <row r="298" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A298" s="13"/>
       <c r="B298" s="14"/>
       <c r="C298" s="14"/>
@@ -7442,11 +7586,11 @@
       <c r="G298" s="14"/>
       <c r="H298" s="14"/>
       <c r="I298" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J298" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K298" s="16"/>
@@ -7454,7 +7598,7 @@
       <c r="M298" s="16"/>
       <c r="N298" s="17"/>
     </row>
-    <row r="299" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A299" s="13"/>
       <c r="B299" s="14"/>
       <c r="C299" s="14"/>
@@ -7464,11 +7608,11 @@
       <c r="G299" s="14"/>
       <c r="H299" s="14"/>
       <c r="I299" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J299" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K299" s="16"/>
@@ -7476,7 +7620,7 @@
       <c r="M299" s="16"/>
       <c r="N299" s="17"/>
     </row>
-    <row r="300" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A300" s="13"/>
       <c r="B300" s="14"/>
       <c r="C300" s="14"/>
@@ -7486,11 +7630,11 @@
       <c r="G300" s="14"/>
       <c r="H300" s="14"/>
       <c r="I300" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J300" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K300" s="16"/>
@@ -7498,7 +7642,7 @@
       <c r="M300" s="16"/>
       <c r="N300" s="17"/>
     </row>
-    <row r="301" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A301" s="13"/>
       <c r="B301" s="14"/>
       <c r="C301" s="14"/>
@@ -7508,11 +7652,11 @@
       <c r="G301" s="14"/>
       <c r="H301" s="14"/>
       <c r="I301" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J301" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K301" s="16"/>
@@ -7520,7 +7664,7 @@
       <c r="M301" s="16"/>
       <c r="N301" s="17"/>
     </row>
-    <row r="302" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A302" s="13"/>
       <c r="B302" s="14"/>
       <c r="C302" s="14"/>
@@ -7530,11 +7674,11 @@
       <c r="G302" s="14"/>
       <c r="H302" s="14"/>
       <c r="I302" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J302" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K302" s="16"/>
@@ -7542,7 +7686,7 @@
       <c r="M302" s="16"/>
       <c r="N302" s="17"/>
     </row>
-    <row r="303" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A303" s="13"/>
       <c r="B303" s="14"/>
       <c r="C303" s="14"/>
@@ -7552,11 +7696,11 @@
       <c r="G303" s="14"/>
       <c r="H303" s="14"/>
       <c r="I303" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J303" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K303" s="16"/>
@@ -7564,7 +7708,7 @@
       <c r="M303" s="16"/>
       <c r="N303" s="17"/>
     </row>
-    <row r="304" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A304" s="13"/>
       <c r="B304" s="14"/>
       <c r="C304" s="14"/>
@@ -7574,11 +7718,11 @@
       <c r="G304" s="14"/>
       <c r="H304" s="14"/>
       <c r="I304" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J304" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K304" s="16"/>
@@ -7586,7 +7730,7 @@
       <c r="M304" s="16"/>
       <c r="N304" s="17"/>
     </row>
-    <row r="305" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A305" s="13"/>
       <c r="B305" s="14"/>
       <c r="C305" s="14"/>
@@ -7596,11 +7740,11 @@
       <c r="G305" s="14"/>
       <c r="H305" s="14"/>
       <c r="I305" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J305" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K305" s="16"/>
@@ -7608,7 +7752,7 @@
       <c r="M305" s="16"/>
       <c r="N305" s="17"/>
     </row>
-    <row r="306" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A306" s="13"/>
       <c r="B306" s="14"/>
       <c r="C306" s="14"/>
@@ -7618,11 +7762,11 @@
       <c r="G306" s="14"/>
       <c r="H306" s="14"/>
       <c r="I306" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J306" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K306" s="16"/>
@@ -7630,7 +7774,7 @@
       <c r="M306" s="16"/>
       <c r="N306" s="17"/>
     </row>
-    <row r="307" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A307" s="13"/>
       <c r="B307" s="14"/>
       <c r="C307" s="14"/>
@@ -7640,11 +7784,11 @@
       <c r="G307" s="14"/>
       <c r="H307" s="14"/>
       <c r="I307" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J307" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K307" s="16"/>
@@ -7652,7 +7796,7 @@
       <c r="M307" s="16"/>
       <c r="N307" s="17"/>
     </row>
-    <row r="308" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A308" s="13"/>
       <c r="B308" s="14"/>
       <c r="C308" s="14"/>
@@ -7662,11 +7806,11 @@
       <c r="G308" s="14"/>
       <c r="H308" s="14"/>
       <c r="I308" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J308" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K308" s="16"/>
@@ -7674,7 +7818,7 @@
       <c r="M308" s="16"/>
       <c r="N308" s="17"/>
     </row>
-    <row r="309" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A309" s="13"/>
       <c r="B309" s="14"/>
       <c r="C309" s="14"/>
@@ -7684,11 +7828,11 @@
       <c r="G309" s="14"/>
       <c r="H309" s="14"/>
       <c r="I309" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J309" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K309" s="16"/>
@@ -7696,7 +7840,7 @@
       <c r="M309" s="16"/>
       <c r="N309" s="17"/>
     </row>
-    <row r="310" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A310" s="13"/>
       <c r="B310" s="14"/>
       <c r="C310" s="14"/>
@@ -7706,11 +7850,11 @@
       <c r="G310" s="14"/>
       <c r="H310" s="14"/>
       <c r="I310" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J310" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K310" s="16"/>
@@ -7718,7 +7862,7 @@
       <c r="M310" s="16"/>
       <c r="N310" s="17"/>
     </row>
-    <row r="311" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A311" s="13"/>
       <c r="B311" s="14"/>
       <c r="C311" s="14"/>
@@ -7728,11 +7872,11 @@
       <c r="G311" s="14"/>
       <c r="H311" s="14"/>
       <c r="I311" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J311" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K311" s="16"/>
@@ -7740,7 +7884,7 @@
       <c r="M311" s="16"/>
       <c r="N311" s="17"/>
     </row>
-    <row r="312" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A312" s="13"/>
       <c r="B312" s="14"/>
       <c r="C312" s="14"/>
@@ -7750,11 +7894,11 @@
       <c r="G312" s="14"/>
       <c r="H312" s="14"/>
       <c r="I312" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J312" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K312" s="16"/>
@@ -7762,7 +7906,7 @@
       <c r="M312" s="16"/>
       <c r="N312" s="17"/>
     </row>
-    <row r="313" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A313" s="13"/>
       <c r="B313" s="14"/>
       <c r="C313" s="14"/>
@@ -7772,11 +7916,11 @@
       <c r="G313" s="14"/>
       <c r="H313" s="14"/>
       <c r="I313" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J313" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K313" s="16"/>
@@ -7784,7 +7928,7 @@
       <c r="M313" s="16"/>
       <c r="N313" s="17"/>
     </row>
-    <row r="314" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A314" s="13"/>
       <c r="B314" s="14"/>
       <c r="C314" s="14"/>
@@ -7794,11 +7938,11 @@
       <c r="G314" s="14"/>
       <c r="H314" s="14"/>
       <c r="I314" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J314" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K314" s="16"/>
@@ -7806,7 +7950,7 @@
       <c r="M314" s="16"/>
       <c r="N314" s="17"/>
     </row>
-    <row r="315" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A315" s="13"/>
       <c r="B315" s="14"/>
       <c r="C315" s="14"/>
@@ -7816,11 +7960,11 @@
       <c r="G315" s="14"/>
       <c r="H315" s="14"/>
       <c r="I315" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J315" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K315" s="16"/>
@@ -7828,7 +7972,7 @@
       <c r="M315" s="16"/>
       <c r="N315" s="17"/>
     </row>
-    <row r="316" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A316" s="13"/>
       <c r="B316" s="14"/>
       <c r="C316" s="14"/>
@@ -7838,11 +7982,11 @@
       <c r="G316" s="14"/>
       <c r="H316" s="14"/>
       <c r="I316" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J316" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K316" s="16"/>
@@ -7850,7 +7994,7 @@
       <c r="M316" s="16"/>
       <c r="N316" s="17"/>
     </row>
-    <row r="317" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A317" s="13"/>
       <c r="B317" s="14"/>
       <c r="C317" s="14"/>
@@ -7860,11 +8004,11 @@
       <c r="G317" s="14"/>
       <c r="H317" s="14"/>
       <c r="I317" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J317" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K317" s="16"/>
@@ -7872,7 +8016,7 @@
       <c r="M317" s="16"/>
       <c r="N317" s="17"/>
     </row>
-    <row r="318" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A318" s="13"/>
       <c r="B318" s="14"/>
       <c r="C318" s="14"/>
@@ -7882,11 +8026,11 @@
       <c r="G318" s="14"/>
       <c r="H318" s="14"/>
       <c r="I318" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J318" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K318" s="16"/>
@@ -7894,7 +8038,7 @@
       <c r="M318" s="16"/>
       <c r="N318" s="17"/>
     </row>
-    <row r="319" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A319" s="13"/>
       <c r="B319" s="14"/>
       <c r="C319" s="14"/>
@@ -7904,11 +8048,11 @@
       <c r="G319" s="14"/>
       <c r="H319" s="14"/>
       <c r="I319" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J319" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K319" s="16"/>
@@ -7916,7 +8060,7 @@
       <c r="M319" s="16"/>
       <c r="N319" s="17"/>
     </row>
-    <row r="320" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A320" s="13"/>
       <c r="B320" s="14"/>
       <c r="C320" s="14"/>
@@ -7926,11 +8070,11 @@
       <c r="G320" s="14"/>
       <c r="H320" s="14"/>
       <c r="I320" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J320" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K320" s="16"/>
@@ -7938,7 +8082,7 @@
       <c r="M320" s="16"/>
       <c r="N320" s="17"/>
     </row>
-    <row r="321" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A321" s="13"/>
       <c r="B321" s="14"/>
       <c r="C321" s="14"/>
@@ -7948,11 +8092,11 @@
       <c r="G321" s="14"/>
       <c r="H321" s="14"/>
       <c r="I321" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J321" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K321" s="16"/>
@@ -7960,7 +8104,7 @@
       <c r="M321" s="16"/>
       <c r="N321" s="17"/>
     </row>
-    <row r="322" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A322" s="13"/>
       <c r="B322" s="14"/>
       <c r="C322" s="14"/>
@@ -7970,11 +8114,11 @@
       <c r="G322" s="14"/>
       <c r="H322" s="14"/>
       <c r="I322" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J322" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K322" s="16"/>
@@ -7982,7 +8126,7 @@
       <c r="M322" s="16"/>
       <c r="N322" s="17"/>
     </row>
-    <row r="323" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A323" s="13"/>
       <c r="B323" s="14"/>
       <c r="C323" s="14"/>
@@ -7992,11 +8136,11 @@
       <c r="G323" s="14"/>
       <c r="H323" s="14"/>
       <c r="I323" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J323" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K323" s="16"/>
@@ -8004,7 +8148,7 @@
       <c r="M323" s="16"/>
       <c r="N323" s="17"/>
     </row>
-    <row r="324" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A324" s="13"/>
       <c r="B324" s="14"/>
       <c r="C324" s="14"/>
@@ -8014,11 +8158,11 @@
       <c r="G324" s="14"/>
       <c r="H324" s="14"/>
       <c r="I324" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J324" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K324" s="16"/>
@@ -8026,7 +8170,7 @@
       <c r="M324" s="16"/>
       <c r="N324" s="17"/>
     </row>
-    <row r="325" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A325" s="13"/>
       <c r="B325" s="14"/>
       <c r="C325" s="14"/>
@@ -8036,11 +8180,11 @@
       <c r="G325" s="14"/>
       <c r="H325" s="14"/>
       <c r="I325" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J325" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K325" s="16"/>
@@ -8048,7 +8192,7 @@
       <c r="M325" s="16"/>
       <c r="N325" s="17"/>
     </row>
-    <row r="326" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A326" s="13"/>
       <c r="B326" s="14"/>
       <c r="C326" s="14"/>
@@ -8058,11 +8202,11 @@
       <c r="G326" s="14"/>
       <c r="H326" s="14"/>
       <c r="I326" s="15" t="str">
-        <f t="shared" ref="I326:I389" si="10">IF(SUM(B326:F326,H326)=0,"",SUM(B326:F326,H326))</f>
+        <f t="shared" ref="I326:I389" si="12">IF(SUM(B326:F326,H326)=0,"",SUM(B326:F326,H326))</f>
         <v/>
       </c>
       <c r="J326" s="15" t="str">
-        <f t="shared" ref="J326:J389" si="11">IF(I326="","",1440-I326)</f>
+        <f t="shared" ref="J326:J389" si="13">IF(I326="","",1440-I326)</f>
         <v/>
       </c>
       <c r="K326" s="16"/>
@@ -8070,7 +8214,7 @@
       <c r="M326" s="16"/>
       <c r="N326" s="17"/>
     </row>
-    <row r="327" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A327" s="13"/>
       <c r="B327" s="14"/>
       <c r="C327" s="14"/>
@@ -8080,11 +8224,11 @@
       <c r="G327" s="14"/>
       <c r="H327" s="14"/>
       <c r="I327" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J327" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K327" s="16"/>
@@ -8092,7 +8236,7 @@
       <c r="M327" s="16"/>
       <c r="N327" s="17"/>
     </row>
-    <row r="328" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A328" s="13"/>
       <c r="B328" s="14"/>
       <c r="C328" s="14"/>
@@ -8102,11 +8246,11 @@
       <c r="G328" s="14"/>
       <c r="H328" s="14"/>
       <c r="I328" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J328" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K328" s="16"/>
@@ -8114,7 +8258,7 @@
       <c r="M328" s="16"/>
       <c r="N328" s="17"/>
     </row>
-    <row r="329" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A329" s="13"/>
       <c r="B329" s="14"/>
       <c r="C329" s="14"/>
@@ -8124,11 +8268,11 @@
       <c r="G329" s="14"/>
       <c r="H329" s="14"/>
       <c r="I329" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J329" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K329" s="16"/>
@@ -8136,7 +8280,7 @@
       <c r="M329" s="16"/>
       <c r="N329" s="17"/>
     </row>
-    <row r="330" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A330" s="13"/>
       <c r="B330" s="14"/>
       <c r="C330" s="14"/>
@@ -8146,11 +8290,11 @@
       <c r="G330" s="14"/>
       <c r="H330" s="14"/>
       <c r="I330" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J330" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K330" s="16"/>
@@ -8158,7 +8302,7 @@
       <c r="M330" s="16"/>
       <c r="N330" s="17"/>
     </row>
-    <row r="331" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A331" s="13"/>
       <c r="B331" s="14"/>
       <c r="C331" s="14"/>
@@ -8168,11 +8312,11 @@
       <c r="G331" s="14"/>
       <c r="H331" s="14"/>
       <c r="I331" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J331" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K331" s="16"/>
@@ -8180,7 +8324,7 @@
       <c r="M331" s="16"/>
       <c r="N331" s="17"/>
     </row>
-    <row r="332" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A332" s="13"/>
       <c r="B332" s="14"/>
       <c r="C332" s="14"/>
@@ -8190,11 +8334,11 @@
       <c r="G332" s="14"/>
       <c r="H332" s="14"/>
       <c r="I332" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J332" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K332" s="16"/>
@@ -8202,7 +8346,7 @@
       <c r="M332" s="16"/>
       <c r="N332" s="17"/>
     </row>
-    <row r="333" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A333" s="13"/>
       <c r="B333" s="14"/>
       <c r="C333" s="14"/>
@@ -8212,11 +8356,11 @@
       <c r="G333" s="14"/>
       <c r="H333" s="14"/>
       <c r="I333" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J333" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K333" s="16"/>
@@ -8224,7 +8368,7 @@
       <c r="M333" s="16"/>
       <c r="N333" s="17"/>
     </row>
-    <row r="334" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A334" s="13"/>
       <c r="B334" s="14"/>
       <c r="C334" s="14"/>
@@ -8234,11 +8378,11 @@
       <c r="G334" s="14"/>
       <c r="H334" s="14"/>
       <c r="I334" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J334" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K334" s="16"/>
@@ -8246,7 +8390,7 @@
       <c r="M334" s="16"/>
       <c r="N334" s="17"/>
     </row>
-    <row r="335" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A335" s="13"/>
       <c r="B335" s="14"/>
       <c r="C335" s="14"/>
@@ -8256,11 +8400,11 @@
       <c r="G335" s="14"/>
       <c r="H335" s="14"/>
       <c r="I335" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J335" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K335" s="16"/>
@@ -8268,7 +8412,7 @@
       <c r="M335" s="16"/>
       <c r="N335" s="17"/>
     </row>
-    <row r="336" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A336" s="13"/>
       <c r="B336" s="14"/>
       <c r="C336" s="14"/>
@@ -8278,11 +8422,11 @@
       <c r="G336" s="14"/>
       <c r="H336" s="14"/>
       <c r="I336" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J336" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K336" s="16"/>
@@ -8290,7 +8434,7 @@
       <c r="M336" s="16"/>
       <c r="N336" s="17"/>
     </row>
-    <row r="337" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A337" s="13"/>
       <c r="B337" s="14"/>
       <c r="C337" s="14"/>
@@ -8300,11 +8444,11 @@
       <c r="G337" s="14"/>
       <c r="H337" s="14"/>
       <c r="I337" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J337" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K337" s="16"/>
@@ -8312,7 +8456,7 @@
       <c r="M337" s="16"/>
       <c r="N337" s="17"/>
     </row>
-    <row r="338" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A338" s="13"/>
       <c r="B338" s="14"/>
       <c r="C338" s="14"/>
@@ -8322,11 +8466,11 @@
       <c r="G338" s="14"/>
       <c r="H338" s="14"/>
       <c r="I338" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J338" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K338" s="16"/>
@@ -8334,7 +8478,7 @@
       <c r="M338" s="16"/>
       <c r="N338" s="17"/>
     </row>
-    <row r="339" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A339" s="13"/>
       <c r="B339" s="14"/>
       <c r="C339" s="14"/>
@@ -8344,11 +8488,11 @@
       <c r="G339" s="14"/>
       <c r="H339" s="14"/>
       <c r="I339" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J339" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K339" s="16"/>
@@ -8356,7 +8500,7 @@
       <c r="M339" s="16"/>
       <c r="N339" s="17"/>
     </row>
-    <row r="340" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A340" s="13"/>
       <c r="B340" s="14"/>
       <c r="C340" s="14"/>
@@ -8366,11 +8510,11 @@
       <c r="G340" s="14"/>
       <c r="H340" s="14"/>
       <c r="I340" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J340" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K340" s="16"/>
@@ -8378,7 +8522,7 @@
       <c r="M340" s="16"/>
       <c r="N340" s="17"/>
     </row>
-    <row r="341" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A341" s="13"/>
       <c r="B341" s="14"/>
       <c r="C341" s="14"/>
@@ -8388,11 +8532,11 @@
       <c r="G341" s="14"/>
       <c r="H341" s="14"/>
       <c r="I341" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J341" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K341" s="16"/>
@@ -8400,7 +8544,7 @@
       <c r="M341" s="16"/>
       <c r="N341" s="17"/>
     </row>
-    <row r="342" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A342" s="13"/>
       <c r="B342" s="14"/>
       <c r="C342" s="14"/>
@@ -8410,11 +8554,11 @@
       <c r="G342" s="14"/>
       <c r="H342" s="14"/>
       <c r="I342" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J342" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K342" s="16"/>
@@ -8422,7 +8566,7 @@
       <c r="M342" s="16"/>
       <c r="N342" s="17"/>
     </row>
-    <row r="343" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A343" s="13"/>
       <c r="B343" s="14"/>
       <c r="C343" s="14"/>
@@ -8432,11 +8576,11 @@
       <c r="G343" s="14"/>
       <c r="H343" s="14"/>
       <c r="I343" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J343" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K343" s="16"/>
@@ -8444,7 +8588,7 @@
       <c r="M343" s="16"/>
       <c r="N343" s="17"/>
     </row>
-    <row r="344" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A344" s="13"/>
       <c r="B344" s="14"/>
       <c r="C344" s="14"/>
@@ -8454,11 +8598,11 @@
       <c r="G344" s="14"/>
       <c r="H344" s="14"/>
       <c r="I344" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J344" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K344" s="16"/>
@@ -8466,7 +8610,7 @@
       <c r="M344" s="16"/>
       <c r="N344" s="17"/>
     </row>
-    <row r="345" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A345" s="13"/>
       <c r="B345" s="14"/>
       <c r="C345" s="14"/>
@@ -8476,11 +8620,11 @@
       <c r="G345" s="14"/>
       <c r="H345" s="14"/>
       <c r="I345" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J345" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K345" s="16"/>
@@ -8488,7 +8632,7 @@
       <c r="M345" s="16"/>
       <c r="N345" s="17"/>
     </row>
-    <row r="346" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A346" s="13"/>
       <c r="B346" s="14"/>
       <c r="C346" s="14"/>
@@ -8498,11 +8642,11 @@
       <c r="G346" s="14"/>
       <c r="H346" s="14"/>
       <c r="I346" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J346" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K346" s="16"/>
@@ -8510,7 +8654,7 @@
       <c r="M346" s="16"/>
       <c r="N346" s="17"/>
     </row>
-    <row r="347" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A347" s="13"/>
       <c r="B347" s="14"/>
       <c r="C347" s="14"/>
@@ -8520,11 +8664,11 @@
       <c r="G347" s="14"/>
       <c r="H347" s="14"/>
       <c r="I347" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J347" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K347" s="16"/>
@@ -8532,7 +8676,7 @@
       <c r="M347" s="16"/>
       <c r="N347" s="17"/>
     </row>
-    <row r="348" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A348" s="13"/>
       <c r="B348" s="14"/>
       <c r="C348" s="14"/>
@@ -8542,11 +8686,11 @@
       <c r="G348" s="14"/>
       <c r="H348" s="14"/>
       <c r="I348" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J348" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K348" s="16"/>
@@ -8554,7 +8698,7 @@
       <c r="M348" s="16"/>
       <c r="N348" s="17"/>
     </row>
-    <row r="349" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A349" s="13"/>
       <c r="B349" s="14"/>
       <c r="C349" s="14"/>
@@ -8564,11 +8708,11 @@
       <c r="G349" s="14"/>
       <c r="H349" s="14"/>
       <c r="I349" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J349" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K349" s="16"/>
@@ -8576,7 +8720,7 @@
       <c r="M349" s="16"/>
       <c r="N349" s="17"/>
     </row>
-    <row r="350" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A350" s="13"/>
       <c r="B350" s="14"/>
       <c r="C350" s="14"/>
@@ -8586,11 +8730,11 @@
       <c r="G350" s="14"/>
       <c r="H350" s="14"/>
       <c r="I350" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J350" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K350" s="16"/>
@@ -8598,7 +8742,7 @@
       <c r="M350" s="16"/>
       <c r="N350" s="17"/>
     </row>
-    <row r="351" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A351" s="13"/>
       <c r="B351" s="14"/>
       <c r="C351" s="14"/>
@@ -8608,11 +8752,11 @@
       <c r="G351" s="14"/>
       <c r="H351" s="14"/>
       <c r="I351" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J351" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K351" s="16"/>
@@ -8620,7 +8764,7 @@
       <c r="M351" s="16"/>
       <c r="N351" s="17"/>
     </row>
-    <row r="352" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A352" s="13"/>
       <c r="B352" s="14"/>
       <c r="C352" s="14"/>
@@ -8630,11 +8774,11 @@
       <c r="G352" s="14"/>
       <c r="H352" s="14"/>
       <c r="I352" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J352" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K352" s="16"/>
@@ -8642,7 +8786,7 @@
       <c r="M352" s="16"/>
       <c r="N352" s="17"/>
     </row>
-    <row r="353" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A353" s="13"/>
       <c r="B353" s="14"/>
       <c r="C353" s="14"/>
@@ -8652,11 +8796,11 @@
       <c r="G353" s="14"/>
       <c r="H353" s="14"/>
       <c r="I353" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J353" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K353" s="16"/>
@@ -8664,7 +8808,7 @@
       <c r="M353" s="16"/>
       <c r="N353" s="17"/>
     </row>
-    <row r="354" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A354" s="13"/>
       <c r="B354" s="14"/>
       <c r="C354" s="14"/>
@@ -8674,11 +8818,11 @@
       <c r="G354" s="14"/>
       <c r="H354" s="14"/>
       <c r="I354" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J354" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K354" s="16"/>
@@ -8686,7 +8830,7 @@
       <c r="M354" s="16"/>
       <c r="N354" s="17"/>
     </row>
-    <row r="355" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A355" s="13"/>
       <c r="B355" s="14"/>
       <c r="C355" s="14"/>
@@ -8696,11 +8840,11 @@
       <c r="G355" s="14"/>
       <c r="H355" s="14"/>
       <c r="I355" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J355" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K355" s="16"/>
@@ -8708,7 +8852,7 @@
       <c r="M355" s="16"/>
       <c r="N355" s="17"/>
     </row>
-    <row r="356" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A356" s="13"/>
       <c r="B356" s="14"/>
       <c r="C356" s="14"/>
@@ -8718,11 +8862,11 @@
       <c r="G356" s="14"/>
       <c r="H356" s="14"/>
       <c r="I356" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J356" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K356" s="16"/>
@@ -8730,7 +8874,7 @@
       <c r="M356" s="16"/>
       <c r="N356" s="17"/>
     </row>
-    <row r="357" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A357" s="13"/>
       <c r="B357" s="14"/>
       <c r="C357" s="14"/>
@@ -8740,11 +8884,11 @@
       <c r="G357" s="14"/>
       <c r="H357" s="14"/>
       <c r="I357" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J357" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K357" s="16"/>
@@ -8752,7 +8896,7 @@
       <c r="M357" s="16"/>
       <c r="N357" s="17"/>
     </row>
-    <row r="358" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A358" s="13"/>
       <c r="B358" s="14"/>
       <c r="C358" s="14"/>
@@ -8762,11 +8906,11 @@
       <c r="G358" s="14"/>
       <c r="H358" s="14"/>
       <c r="I358" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J358" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K358" s="16"/>
@@ -8774,7 +8918,7 @@
       <c r="M358" s="16"/>
       <c r="N358" s="17"/>
     </row>
-    <row r="359" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A359" s="13"/>
       <c r="B359" s="14"/>
       <c r="C359" s="14"/>
@@ -8784,11 +8928,11 @@
       <c r="G359" s="14"/>
       <c r="H359" s="14"/>
       <c r="I359" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J359" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K359" s="16"/>
@@ -8796,7 +8940,7 @@
       <c r="M359" s="16"/>
       <c r="N359" s="17"/>
     </row>
-    <row r="360" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A360" s="13"/>
       <c r="B360" s="14"/>
       <c r="C360" s="14"/>
@@ -8806,11 +8950,11 @@
       <c r="G360" s="14"/>
       <c r="H360" s="14"/>
       <c r="I360" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J360" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K360" s="16"/>
@@ -8818,7 +8962,7 @@
       <c r="M360" s="16"/>
       <c r="N360" s="17"/>
     </row>
-    <row r="361" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A361" s="13"/>
       <c r="B361" s="14"/>
       <c r="C361" s="14"/>
@@ -8828,11 +8972,11 @@
       <c r="G361" s="14"/>
       <c r="H361" s="14"/>
       <c r="I361" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J361" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K361" s="16"/>
@@ -8840,7 +8984,7 @@
       <c r="M361" s="16"/>
       <c r="N361" s="17"/>
     </row>
-    <row r="362" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A362" s="13"/>
       <c r="B362" s="14"/>
       <c r="C362" s="14"/>
@@ -8850,11 +8994,11 @@
       <c r="G362" s="14"/>
       <c r="H362" s="14"/>
       <c r="I362" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J362" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K362" s="16"/>
@@ -8862,7 +9006,7 @@
       <c r="M362" s="16"/>
       <c r="N362" s="17"/>
     </row>
-    <row r="363" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A363" s="13"/>
       <c r="B363" s="14"/>
       <c r="C363" s="14"/>
@@ -8872,11 +9016,11 @@
       <c r="G363" s="14"/>
       <c r="H363" s="14"/>
       <c r="I363" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J363" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K363" s="16"/>
@@ -8884,7 +9028,7 @@
       <c r="M363" s="16"/>
       <c r="N363" s="17"/>
     </row>
-    <row r="364" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A364" s="13"/>
       <c r="B364" s="14"/>
       <c r="C364" s="14"/>
@@ -8894,11 +9038,11 @@
       <c r="G364" s="14"/>
       <c r="H364" s="14"/>
       <c r="I364" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J364" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K364" s="16"/>
@@ -8906,7 +9050,7 @@
       <c r="M364" s="16"/>
       <c r="N364" s="17"/>
     </row>
-    <row r="365" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A365" s="13"/>
       <c r="B365" s="14"/>
       <c r="C365" s="14"/>
@@ -8916,11 +9060,11 @@
       <c r="G365" s="14"/>
       <c r="H365" s="14"/>
       <c r="I365" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J365" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K365" s="16"/>
@@ -8928,7 +9072,7 @@
       <c r="M365" s="16"/>
       <c r="N365" s="17"/>
     </row>
-    <row r="366" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A366" s="13"/>
       <c r="B366" s="14"/>
       <c r="C366" s="14"/>
@@ -8938,11 +9082,11 @@
       <c r="G366" s="14"/>
       <c r="H366" s="14"/>
       <c r="I366" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J366" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K366" s="16"/>
@@ -8950,7 +9094,7 @@
       <c r="M366" s="16"/>
       <c r="N366" s="17"/>
     </row>
-    <row r="367" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A367" s="13"/>
       <c r="B367" s="14"/>
       <c r="C367" s="14"/>
@@ -8960,11 +9104,11 @@
       <c r="G367" s="14"/>
       <c r="H367" s="14"/>
       <c r="I367" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J367" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K367" s="16"/>
@@ -8972,7 +9116,7 @@
       <c r="M367" s="16"/>
       <c r="N367" s="17"/>
     </row>
-    <row r="368" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A368" s="13"/>
       <c r="B368" s="14"/>
       <c r="C368" s="14"/>
@@ -8982,11 +9126,11 @@
       <c r="G368" s="14"/>
       <c r="H368" s="14"/>
       <c r="I368" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J368" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K368" s="16"/>
@@ -8994,7 +9138,7 @@
       <c r="M368" s="16"/>
       <c r="N368" s="17"/>
     </row>
-    <row r="369" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A369" s="13"/>
       <c r="B369" s="14"/>
       <c r="C369" s="14"/>
@@ -9004,11 +9148,11 @@
       <c r="G369" s="14"/>
       <c r="H369" s="14"/>
       <c r="I369" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J369" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K369" s="16"/>
@@ -9016,7 +9160,7 @@
       <c r="M369" s="16"/>
       <c r="N369" s="17"/>
     </row>
-    <row r="370" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A370" s="13"/>
       <c r="B370" s="14"/>
       <c r="C370" s="14"/>
@@ -9026,11 +9170,11 @@
       <c r="G370" s="14"/>
       <c r="H370" s="14"/>
       <c r="I370" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J370" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K370" s="16"/>
@@ -9038,7 +9182,7 @@
       <c r="M370" s="16"/>
       <c r="N370" s="17"/>
     </row>
-    <row r="371" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A371" s="13"/>
       <c r="B371" s="14"/>
       <c r="C371" s="14"/>
@@ -9048,11 +9192,11 @@
       <c r="G371" s="14"/>
       <c r="H371" s="14"/>
       <c r="I371" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J371" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K371" s="16"/>
@@ -9060,7 +9204,7 @@
       <c r="M371" s="16"/>
       <c r="N371" s="17"/>
     </row>
-    <row r="372" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A372" s="13"/>
       <c r="B372" s="14"/>
       <c r="C372" s="14"/>
@@ -9070,11 +9214,11 @@
       <c r="G372" s="14"/>
       <c r="H372" s="14"/>
       <c r="I372" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J372" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K372" s="16"/>
@@ -9082,7 +9226,7 @@
       <c r="M372" s="16"/>
       <c r="N372" s="17"/>
     </row>
-    <row r="373" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A373" s="13"/>
       <c r="B373" s="14"/>
       <c r="C373" s="14"/>
@@ -9092,11 +9236,11 @@
       <c r="G373" s="14"/>
       <c r="H373" s="14"/>
       <c r="I373" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J373" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K373" s="16"/>
@@ -9104,7 +9248,7 @@
       <c r="M373" s="16"/>
       <c r="N373" s="17"/>
     </row>
-    <row r="374" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A374" s="13"/>
       <c r="B374" s="14"/>
       <c r="C374" s="14"/>
@@ -9114,11 +9258,11 @@
       <c r="G374" s="14"/>
       <c r="H374" s="14"/>
       <c r="I374" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J374" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K374" s="16"/>
@@ -9126,7 +9270,7 @@
       <c r="M374" s="16"/>
       <c r="N374" s="17"/>
     </row>
-    <row r="375" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A375" s="13"/>
       <c r="B375" s="14"/>
       <c r="C375" s="14"/>
@@ -9136,11 +9280,11 @@
       <c r="G375" s="14"/>
       <c r="H375" s="14"/>
       <c r="I375" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J375" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K375" s="16"/>
@@ -9148,7 +9292,7 @@
       <c r="M375" s="16"/>
       <c r="N375" s="17"/>
     </row>
-    <row r="376" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A376" s="13"/>
       <c r="B376" s="14"/>
       <c r="C376" s="14"/>
@@ -9158,11 +9302,11 @@
       <c r="G376" s="14"/>
       <c r="H376" s="14"/>
       <c r="I376" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J376" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K376" s="16"/>
@@ -9170,7 +9314,7 @@
       <c r="M376" s="16"/>
       <c r="N376" s="17"/>
     </row>
-    <row r="377" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A377" s="13"/>
       <c r="B377" s="14"/>
       <c r="C377" s="14"/>
@@ -9180,11 +9324,11 @@
       <c r="G377" s="14"/>
       <c r="H377" s="14"/>
       <c r="I377" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J377" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K377" s="16"/>
@@ -9192,7 +9336,7 @@
       <c r="M377" s="16"/>
       <c r="N377" s="17"/>
     </row>
-    <row r="378" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A378" s="13"/>
       <c r="B378" s="14"/>
       <c r="C378" s="14"/>
@@ -9202,11 +9346,11 @@
       <c r="G378" s="14"/>
       <c r="H378" s="14"/>
       <c r="I378" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J378" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K378" s="16"/>
@@ -9214,7 +9358,7 @@
       <c r="M378" s="16"/>
       <c r="N378" s="17"/>
     </row>
-    <row r="379" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A379" s="13"/>
       <c r="B379" s="14"/>
       <c r="C379" s="14"/>
@@ -9224,11 +9368,11 @@
       <c r="G379" s="14"/>
       <c r="H379" s="14"/>
       <c r="I379" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J379" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K379" s="16"/>
@@ -9236,7 +9380,7 @@
       <c r="M379" s="16"/>
       <c r="N379" s="17"/>
     </row>
-    <row r="380" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A380" s="13"/>
       <c r="B380" s="14"/>
       <c r="C380" s="14"/>
@@ -9246,11 +9390,11 @@
       <c r="G380" s="14"/>
       <c r="H380" s="14"/>
       <c r="I380" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J380" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K380" s="16"/>
@@ -9258,7 +9402,7 @@
       <c r="M380" s="16"/>
       <c r="N380" s="17"/>
     </row>
-    <row r="381" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A381" s="13"/>
       <c r="B381" s="14"/>
       <c r="C381" s="14"/>
@@ -9268,11 +9412,11 @@
       <c r="G381" s="14"/>
       <c r="H381" s="14"/>
       <c r="I381" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J381" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K381" s="16"/>
@@ -9280,7 +9424,7 @@
       <c r="M381" s="16"/>
       <c r="N381" s="17"/>
     </row>
-    <row r="382" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A382" s="13"/>
       <c r="B382" s="14"/>
       <c r="C382" s="14"/>
@@ -9290,11 +9434,11 @@
       <c r="G382" s="14"/>
       <c r="H382" s="14"/>
       <c r="I382" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J382" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K382" s="16"/>
@@ -9302,7 +9446,7 @@
       <c r="M382" s="16"/>
       <c r="N382" s="17"/>
     </row>
-    <row r="383" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A383" s="13"/>
       <c r="B383" s="14"/>
       <c r="C383" s="14"/>
@@ -9312,11 +9456,11 @@
       <c r="G383" s="14"/>
       <c r="H383" s="14"/>
       <c r="I383" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J383" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K383" s="16"/>
@@ -9324,7 +9468,7 @@
       <c r="M383" s="16"/>
       <c r="N383" s="17"/>
     </row>
-    <row r="384" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A384" s="13"/>
       <c r="B384" s="14"/>
       <c r="C384" s="14"/>
@@ -9334,11 +9478,11 @@
       <c r="G384" s="14"/>
       <c r="H384" s="14"/>
       <c r="I384" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J384" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K384" s="16"/>
@@ -9346,7 +9490,7 @@
       <c r="M384" s="16"/>
       <c r="N384" s="17"/>
     </row>
-    <row r="385" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A385" s="13"/>
       <c r="B385" s="14"/>
       <c r="C385" s="14"/>
@@ -9356,11 +9500,11 @@
       <c r="G385" s="14"/>
       <c r="H385" s="14"/>
       <c r="I385" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J385" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K385" s="16"/>
@@ -9368,7 +9512,7 @@
       <c r="M385" s="16"/>
       <c r="N385" s="17"/>
     </row>
-    <row r="386" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A386" s="13"/>
       <c r="B386" s="14"/>
       <c r="C386" s="14"/>
@@ -9378,11 +9522,11 @@
       <c r="G386" s="14"/>
       <c r="H386" s="14"/>
       <c r="I386" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J386" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K386" s="16"/>
@@ -9390,7 +9534,7 @@
       <c r="M386" s="16"/>
       <c r="N386" s="17"/>
     </row>
-    <row r="387" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A387" s="13"/>
       <c r="B387" s="14"/>
       <c r="C387" s="14"/>
@@ -9400,11 +9544,11 @@
       <c r="G387" s="14"/>
       <c r="H387" s="14"/>
       <c r="I387" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J387" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K387" s="16"/>
@@ -9412,7 +9556,7 @@
       <c r="M387" s="16"/>
       <c r="N387" s="17"/>
     </row>
-    <row r="388" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A388" s="13"/>
       <c r="B388" s="14"/>
       <c r="C388" s="14"/>
@@ -9422,11 +9566,11 @@
       <c r="G388" s="14"/>
       <c r="H388" s="14"/>
       <c r="I388" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J388" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K388" s="16"/>
@@ -9434,7 +9578,7 @@
       <c r="M388" s="16"/>
       <c r="N388" s="17"/>
     </row>
-    <row r="389" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A389" s="13"/>
       <c r="B389" s="14"/>
       <c r="C389" s="14"/>
@@ -9444,11 +9588,11 @@
       <c r="G389" s="14"/>
       <c r="H389" s="14"/>
       <c r="I389" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J389" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K389" s="16"/>
@@ -9456,7 +9600,7 @@
       <c r="M389" s="16"/>
       <c r="N389" s="17"/>
     </row>
-    <row r="390" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A390" s="13"/>
       <c r="B390" s="14"/>
       <c r="C390" s="14"/>
@@ -9466,11 +9610,11 @@
       <c r="G390" s="14"/>
       <c r="H390" s="14"/>
       <c r="I390" s="15" t="str">
-        <f t="shared" ref="I390:I401" si="12">IF(SUM(B390:F390,H390)=0,"",SUM(B390:F390,H390))</f>
+        <f t="shared" ref="I390:I401" si="14">IF(SUM(B390:F390,H390)=0,"",SUM(B390:F390,H390))</f>
         <v/>
       </c>
       <c r="J390" s="15" t="str">
-        <f t="shared" ref="J390:J401" si="13">IF(I390="","",1440-I390)</f>
+        <f t="shared" ref="J390:J401" si="15">IF(I390="","",1440-I390)</f>
         <v/>
       </c>
       <c r="K390" s="16"/>
@@ -9478,7 +9622,7 @@
       <c r="M390" s="16"/>
       <c r="N390" s="17"/>
     </row>
-    <row r="391" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A391" s="13"/>
       <c r="B391" s="14"/>
       <c r="C391" s="14"/>
@@ -9488,11 +9632,11 @@
       <c r="G391" s="14"/>
       <c r="H391" s="14"/>
       <c r="I391" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J391" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K391" s="16"/>
@@ -9500,7 +9644,7 @@
       <c r="M391" s="16"/>
       <c r="N391" s="17"/>
     </row>
-    <row r="392" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A392" s="13"/>
       <c r="B392" s="14"/>
       <c r="C392" s="14"/>
@@ -9510,11 +9654,11 @@
       <c r="G392" s="14"/>
       <c r="H392" s="14"/>
       <c r="I392" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J392" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K392" s="16"/>
@@ -9522,7 +9666,7 @@
       <c r="M392" s="16"/>
       <c r="N392" s="17"/>
     </row>
-    <row r="393" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A393" s="13"/>
       <c r="B393" s="14"/>
       <c r="C393" s="14"/>
@@ -9532,11 +9676,11 @@
       <c r="G393" s="14"/>
       <c r="H393" s="14"/>
       <c r="I393" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J393" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K393" s="16"/>
@@ -9544,7 +9688,7 @@
       <c r="M393" s="16"/>
       <c r="N393" s="17"/>
     </row>
-    <row r="394" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A394" s="13"/>
       <c r="B394" s="14"/>
       <c r="C394" s="14"/>
@@ -9554,11 +9698,11 @@
       <c r="G394" s="14"/>
       <c r="H394" s="14"/>
       <c r="I394" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J394" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K394" s="16"/>
@@ -9566,7 +9710,7 @@
       <c r="M394" s="16"/>
       <c r="N394" s="17"/>
     </row>
-    <row r="395" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A395" s="13"/>
       <c r="B395" s="14"/>
       <c r="C395" s="14"/>
@@ -9576,11 +9720,11 @@
       <c r="G395" s="14"/>
       <c r="H395" s="14"/>
       <c r="I395" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J395" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K395" s="16"/>
@@ -9588,7 +9732,7 @@
       <c r="M395" s="16"/>
       <c r="N395" s="17"/>
     </row>
-    <row r="396" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A396" s="13"/>
       <c r="B396" s="14"/>
       <c r="C396" s="14"/>
@@ -9598,11 +9742,11 @@
       <c r="G396" s="14"/>
       <c r="H396" s="14"/>
       <c r="I396" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J396" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K396" s="16"/>
@@ -9610,7 +9754,7 @@
       <c r="M396" s="16"/>
       <c r="N396" s="17"/>
     </row>
-    <row r="397" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A397" s="13"/>
       <c r="B397" s="14"/>
       <c r="C397" s="14"/>
@@ -9620,11 +9764,11 @@
       <c r="G397" s="14"/>
       <c r="H397" s="14"/>
       <c r="I397" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J397" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K397" s="16"/>
@@ -9632,7 +9776,7 @@
       <c r="M397" s="16"/>
       <c r="N397" s="17"/>
     </row>
-    <row r="398" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A398" s="13"/>
       <c r="B398" s="14"/>
       <c r="C398" s="14"/>
@@ -9642,11 +9786,11 @@
       <c r="G398" s="14"/>
       <c r="H398" s="14"/>
       <c r="I398" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J398" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K398" s="16"/>
@@ -9654,7 +9798,7 @@
       <c r="M398" s="16"/>
       <c r="N398" s="17"/>
     </row>
-    <row r="399" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A399" s="13"/>
       <c r="B399" s="14"/>
       <c r="C399" s="14"/>
@@ -9664,11 +9808,11 @@
       <c r="G399" s="14"/>
       <c r="H399" s="14"/>
       <c r="I399" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J399" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K399" s="16"/>
@@ -9676,7 +9820,7 @@
       <c r="M399" s="16"/>
       <c r="N399" s="17"/>
     </row>
-    <row r="400" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A400" s="13"/>
       <c r="B400" s="14"/>
       <c r="C400" s="14"/>
@@ -9686,11 +9830,11 @@
       <c r="G400" s="14"/>
       <c r="H400" s="14"/>
       <c r="I400" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J400" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K400" s="16"/>
@@ -9698,7 +9842,7 @@
       <c r="M400" s="16"/>
       <c r="N400" s="17"/>
     </row>
-    <row r="401" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A401" s="13"/>
       <c r="B401" s="14"/>
       <c r="C401" s="14"/>
@@ -9708,11 +9852,11 @@
       <c r="G401" s="14"/>
       <c r="H401" s="14"/>
       <c r="I401" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J401" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K401" s="16"/>
